--- a/HDLBits_Tracker.xlsx
+++ b/HDLBits_Tracker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rff753c5e07404c55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="R2073de9ca2e24fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb227a53ac6834bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="Rde6eb7f34cc24e36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2281,7 +2281,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2353,6 +2353,16 @@
         <x:fgColor rgb="FFCCFFCC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E1F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF99"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="7">
     <x:border/>
@@ -2415,7 +2425,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="79">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2610,6 +2620,11 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Hyperlink" xfId="1"/>
@@ -2941,7 +2956,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="33" t="str">
-        <x:v>Day 11 plan</x:v>
+        <x:v>Day 12 plan</x:v>
       </x:c>
       <x:c r="G5" s="33" t="s">
         <x:v>5</x:v>
@@ -2971,7 +2986,7 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="G6" s="62" t="n">
-        <x:v>46207</x:v>
+        <x:v>46208</x:v>
       </x:c>
       <x:c r="H6" s="34"/>
     </x:row>
@@ -2995,7 +3010,7 @@
         <x:v>Queue</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
-        <x:v>study/Day 11.md</x:v>
+        <x:v>study/Day 12.md</x:v>
       </x:c>
       <x:c r="H8" s="35"/>
     </x:row>
@@ -3309,6 +3324,15 @@
       </x:c>
     </x:row>
     <x:row r="22">
+      <x:c r="A22" s="75" t="str">
+        <x:v>Day 12</x:v>
+      </x:c>
+      <x:c r="B22" s="71" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="C22" s="78" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E22" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -3904,7 +3928,7 @@
       <x:c r="A11" s="3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B11" s="3">
+      <x:c r="B11" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
@@ -3922,8 +3946,8 @@
       <x:c r="G11" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H11" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I11" s="56">
         <x:v>46196</x:v>
@@ -3971,7 +3995,7 @@
       <x:c r="A12" s="7">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B12" s="7">
+      <x:c r="B12" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="8" t="s">
@@ -3989,8 +4013,8 @@
       <x:c r="G12" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H12" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H12" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I12" s="55">
         <x:v>46196</x:v>
@@ -4038,7 +4062,7 @@
       <x:c r="A13" s="3">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B13" s="3">
+      <x:c r="B13" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
@@ -4056,8 +4080,8 @@
       <x:c r="G13" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H13" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I13" s="56">
         <x:v>46196</x:v>
@@ -4105,7 +4129,7 @@
       <x:c r="A14" s="7">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B14" s="7">
+      <x:c r="B14" s="7" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
@@ -4123,8 +4147,8 @@
       <x:c r="G14" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H14" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H14" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I14" s="55">
         <x:v>46197</x:v>
@@ -4172,7 +4196,7 @@
       <x:c r="A15" s="3">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B15" s="3">
+      <x:c r="B15" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
@@ -4190,8 +4214,8 @@
       <x:c r="G15" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H15" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I15" s="56">
         <x:v>46197</x:v>
@@ -4239,7 +4263,7 @@
       <x:c r="A16" s="7">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B16" s="7">
+      <x:c r="B16" s="7" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
@@ -4257,8 +4281,8 @@
       <x:c r="G16" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H16" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H16" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I16" s="55">
         <x:v>46197</x:v>
@@ -4306,7 +4330,7 @@
       <x:c r="A17" s="3">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B17" s="3">
+      <x:c r="B17" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
@@ -4324,8 +4348,8 @@
       <x:c r="G17" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H17" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I17" s="56">
         <x:v>46197</x:v>
@@ -4373,7 +4397,7 @@
       <x:c r="A18" s="7">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B18" s="7">
+      <x:c r="B18" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
@@ -4391,8 +4415,8 @@
       <x:c r="G18" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H18" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H18" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I18" s="55">
         <x:v>46196</x:v>
@@ -4465,7 +4489,7 @@
       <x:c r="A20" s="3">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B20" s="3">
+      <x:c r="B20" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
@@ -4483,8 +4507,8 @@
       <x:c r="G20" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H20" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I20" s="56">
         <x:v>46196</x:v>
@@ -4532,7 +4556,7 @@
       <x:c r="A21" s="7">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B21" s="7">
+      <x:c r="B21" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="8" t="s">
@@ -4550,8 +4574,8 @@
       <x:c r="G21" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H21" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H21" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I21" s="55">
         <x:v>46196</x:v>
@@ -4599,7 +4623,7 @@
       <x:c r="A22" s="3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B22" s="3">
+      <x:c r="B22" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
@@ -4617,8 +4641,8 @@
       <x:c r="G22" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H22" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I22" s="56">
         <x:v>46196</x:v>
@@ -4666,7 +4690,7 @@
       <x:c r="A23" s="7">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B23" s="7">
+      <x:c r="B23" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
@@ -4684,8 +4708,8 @@
       <x:c r="G23" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H23" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H23" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I23" s="55">
         <x:v>46196</x:v>
@@ -4733,7 +4757,7 @@
       <x:c r="A24" s="3">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B24" s="3">
+      <x:c r="B24" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
@@ -4751,8 +4775,8 @@
       <x:c r="G24" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H24" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I24" s="56">
         <x:v>46196</x:v>
@@ -4800,7 +4824,7 @@
       <x:c r="A25" s="7">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B25" s="7">
+      <x:c r="B25" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
@@ -4818,8 +4842,8 @@
       <x:c r="G25" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H25" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H25" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I25" s="55">
         <x:v>46196</x:v>
@@ -4867,7 +4891,7 @@
       <x:c r="A26" s="3">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B26" s="3">
+      <x:c r="B26" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
@@ -4885,8 +4909,8 @@
       <x:c r="G26" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H26" s="3" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I26" s="56">
         <x:v>46196</x:v>
@@ -4934,7 +4958,7 @@
       <x:c r="A27" s="7">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B27" s="7">
+      <x:c r="B27" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="8" t="s">
@@ -4952,8 +4976,8 @@
       <x:c r="G27" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H27" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="H27" s="7" t="str">
+        <x:v>Day 01</x:v>
       </x:c>
       <x:c r="I27" s="55">
         <x:v>46196</x:v>
@@ -5001,7 +5025,7 @@
       <x:c r="A28" s="3">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B28" s="3">
+      <x:c r="B28" s="3" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
@@ -5019,8 +5043,8 @@
       <x:c r="G28" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H28" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H28" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I28" s="56">
         <x:v>46197</x:v>
@@ -5093,7 +5117,7 @@
       <x:c r="A30" s="7">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B30" s="7">
+      <x:c r="B30" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
@@ -5111,8 +5135,8 @@
       <x:c r="G30" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H30" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H30" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I30" s="55">
         <x:v>46197</x:v>
@@ -5160,7 +5184,7 @@
       <x:c r="A31" s="3">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B31" s="3">
+      <x:c r="B31" s="3" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
@@ -5178,8 +5202,8 @@
       <x:c r="G31" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H31" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I31" s="56">
         <x:v>46197</x:v>
@@ -5227,7 +5251,7 @@
       <x:c r="A32" s="7">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B32" s="7">
+      <x:c r="B32" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C32" s="8" t="s">
@@ -5245,8 +5269,8 @@
       <x:c r="G32" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H32" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H32" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I32" s="55">
         <x:v>46197</x:v>
@@ -5294,7 +5318,7 @@
       <x:c r="A33" s="3">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B33" s="3">
+      <x:c r="B33" s="3" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="2" t="s">
@@ -5312,8 +5336,8 @@
       <x:c r="G33" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H33" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H33" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I33" s="56">
         <x:v>46197</x:v>
@@ -5361,7 +5385,7 @@
       <x:c r="A34" s="7">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B34" s="7">
+      <x:c r="B34" s="7" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C34" s="8" t="s">
@@ -5379,8 +5403,8 @@
       <x:c r="G34" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H34" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H34" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I34" s="55">
         <x:v>46197</x:v>
@@ -5428,7 +5452,7 @@
       <x:c r="A35" s="3">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B35" s="3">
+      <x:c r="B35" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
@@ -5446,8 +5470,8 @@
       <x:c r="G35" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H35" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H35" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I35" s="56">
         <x:v>46197</x:v>
@@ -5495,7 +5519,7 @@
       <x:c r="A36" s="7">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B36" s="7">
+      <x:c r="B36" s="7" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="8" t="s">
@@ -5513,8 +5537,8 @@
       <x:c r="G36" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H36" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H36" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I36" s="55">
         <x:v>46197</x:v>
@@ -5562,7 +5586,7 @@
       <x:c r="A37" s="3">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B37" s="3">
+      <x:c r="B37" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C37" s="2" t="s">
@@ -5580,8 +5604,8 @@
       <x:c r="G37" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H37" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H37" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I37" s="56">
         <x:v>46197</x:v>
@@ -5629,7 +5653,7 @@
       <x:c r="A38" s="7">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B38" s="7">
+      <x:c r="B38" s="7" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
@@ -5647,8 +5671,8 @@
       <x:c r="G38" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H38" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H38" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I38" s="55">
         <x:v>46197</x:v>
@@ -5721,7 +5745,7 @@
       <x:c r="A40" s="3">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B40" s="3">
+      <x:c r="B40" s="3" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C40" s="2" t="s">
@@ -5739,8 +5763,8 @@
       <x:c r="G40" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H40" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I40" s="56">
         <x:v>46197</x:v>
@@ -5788,7 +5812,7 @@
       <x:c r="A41" s="7">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B41" s="7">
+      <x:c r="B41" s="7" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="C41" s="8" t="s">
@@ -5806,8 +5830,8 @@
       <x:c r="G41" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H41" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H41" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I41" s="55">
         <x:v>46197</x:v>
@@ -5855,7 +5879,7 @@
       <x:c r="A42" s="3">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B42" s="3">
+      <x:c r="B42" s="3" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C42" s="2" t="s">
@@ -5873,8 +5897,8 @@
       <x:c r="G42" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H42" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I42" s="56">
         <x:v>46197</x:v>
@@ -5922,7 +5946,7 @@
       <x:c r="A43" s="7">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B43" s="7">
+      <x:c r="B43" s="7" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
@@ -5940,8 +5964,8 @@
       <x:c r="G43" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H43" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H43" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I43" s="55">
         <x:v>46197</x:v>
@@ -5989,7 +6013,7 @@
       <x:c r="A44" s="3">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B44" s="3">
+      <x:c r="B44" s="3" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="C44" s="2" t="s">
@@ -6007,8 +6031,8 @@
       <x:c r="G44" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H44" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H44" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I44" s="56">
         <x:v>46197</x:v>
@@ -6056,7 +6080,7 @@
       <x:c r="A45" s="7">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B45" s="7">
+      <x:c r="B45" s="7" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="8" t="s">
@@ -6074,8 +6098,8 @@
       <x:c r="G45" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H45" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H45" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I45" s="55">
         <x:v>46197</x:v>
@@ -6123,7 +6147,7 @@
       <x:c r="A46" s="3">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B46" s="3">
+      <x:c r="B46" s="3" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="2" t="s">
@@ -6141,8 +6165,8 @@
       <x:c r="G46" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H46" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I46" s="56">
         <x:v>46197</x:v>
@@ -6190,7 +6214,7 @@
       <x:c r="A47" s="7">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B47" s="7">
+      <x:c r="B47" s="7" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
@@ -6208,8 +6232,8 @@
       <x:c r="G47" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H47" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H47" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I47" s="55">
         <x:v>46197</x:v>
@@ -6282,7 +6306,7 @@
       <x:c r="A49" s="3">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B49" s="3">
+      <x:c r="B49" s="3" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C49" s="2" t="s">
@@ -6300,8 +6324,8 @@
       <x:c r="G49" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H49" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H49" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I49" s="56">
         <x:v>46197</x:v>
@@ -6349,7 +6373,7 @@
       <x:c r="A50" s="7">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B50" s="7">
+      <x:c r="B50" s="7" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
@@ -6367,8 +6391,8 @@
       <x:c r="G50" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H50" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H50" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I50" s="55">
         <x:v>46197</x:v>
@@ -6416,7 +6440,7 @@
       <x:c r="A51" s="3">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B51" s="3">
+      <x:c r="B51" s="3" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C51" s="2" t="s">
@@ -6434,8 +6458,8 @@
       <x:c r="G51" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H51" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H51" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I51" s="56">
         <x:v>46197</x:v>
@@ -6483,7 +6507,7 @@
       <x:c r="A52" s="7">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B52" s="7">
+      <x:c r="B52" s="7" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
@@ -6501,8 +6525,8 @@
       <x:c r="G52" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H52" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H52" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I52" s="55">
         <x:v>46197</x:v>
@@ -6550,7 +6574,7 @@
       <x:c r="A53" s="3">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B53" s="3">
+      <x:c r="B53" s="3" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="2" t="s">
@@ -6568,8 +6592,8 @@
       <x:c r="G53" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H53" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H53" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I53" s="56">
         <x:v>46197</x:v>
@@ -6617,7 +6641,7 @@
       <x:c r="A54" s="7">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B54" s="7">
+      <x:c r="B54" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
@@ -6635,8 +6659,8 @@
       <x:c r="G54" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H54" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H54" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I54" s="55">
         <x:v>46197</x:v>
@@ -6684,7 +6708,7 @@
       <x:c r="A55" s="3">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B55" s="3">
+      <x:c r="B55" s="3" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="C55" s="2" t="s">
@@ -6702,8 +6726,8 @@
       <x:c r="G55" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H55" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H55" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I55" s="56">
         <x:v>46198</x:v>
@@ -6801,7 +6825,7 @@
       <x:c r="A58" s="7">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B58" s="7">
+      <x:c r="B58" s="7" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
@@ -6819,8 +6843,8 @@
       <x:c r="G58" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H58" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H58" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I58" s="55">
         <x:v>46197</x:v>
@@ -6868,7 +6892,7 @@
       <x:c r="A59" s="3">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B59" s="3">
+      <x:c r="B59" s="3" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C59" s="2" t="s">
@@ -6886,8 +6910,8 @@
       <x:c r="G59" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H59" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H59" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I59" s="56">
         <x:v>46197</x:v>
@@ -6935,7 +6959,7 @@
       <x:c r="A60" s="7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B60" s="7">
+      <x:c r="B60" s="7" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
@@ -6953,8 +6977,8 @@
       <x:c r="G60" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H60" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H60" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I60" s="55">
         <x:v>46197</x:v>
@@ -7002,7 +7026,7 @@
       <x:c r="A61" s="3">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B61" s="3">
+      <x:c r="B61" s="3" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C61" s="2" t="s">
@@ -7020,8 +7044,8 @@
       <x:c r="G61" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H61" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H61" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I61" s="56">
         <x:v>46197</x:v>
@@ -7069,7 +7093,7 @@
       <x:c r="A62" s="7">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B62" s="7">
+      <x:c r="B62" s="7" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
@@ -7087,8 +7111,8 @@
       <x:c r="G62" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H62" s="7" t="s">
-        <x:v>16</x:v>
+      <x:c r="H62" s="7" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I62" s="55">
         <x:v>46197</x:v>
@@ -7136,7 +7160,7 @@
       <x:c r="A63" s="3">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B63" s="3">
+      <x:c r="B63" s="3" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C63" s="2" t="s">
@@ -7154,8 +7178,8 @@
       <x:c r="G63" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H63" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H63" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I63" s="56">
         <x:v>46198</x:v>
@@ -7203,7 +7227,7 @@
       <x:c r="A64" s="7">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B64" s="7">
+      <x:c r="B64" s="7" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
@@ -7221,8 +7245,8 @@
       <x:c r="G64" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H64" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H64" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I64" s="55">
         <x:v>46198</x:v>
@@ -7270,7 +7294,7 @@
       <x:c r="A65" s="3">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B65" s="3">
+      <x:c r="B65" s="3" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C65" s="2" t="s">
@@ -7288,8 +7312,8 @@
       <x:c r="G65" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H65" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I65" s="56">
         <x:v>46198</x:v>
@@ -7337,7 +7361,7 @@
       <x:c r="A66" s="7">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B66" s="7">
+      <x:c r="B66" s="7" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
@@ -7355,8 +7379,8 @@
       <x:c r="G66" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H66" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H66" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I66" s="55">
         <x:v>46198</x:v>
@@ -7404,7 +7428,7 @@
       <x:c r="A67" s="3">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B67" s="3">
+      <x:c r="B67" s="3" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C67" s="2" t="s">
@@ -7422,8 +7446,8 @@
       <x:c r="G67" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H67" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H67" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I67" s="56">
         <x:v>46198</x:v>
@@ -7471,7 +7495,7 @@
       <x:c r="A68" s="7">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B68" s="7">
+      <x:c r="B68" s="7" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="C68" s="8" t="s">
@@ -7489,8 +7513,8 @@
       <x:c r="G68" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H68" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H68" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I68" s="55">
         <x:v>46198</x:v>
@@ -7538,7 +7562,7 @@
       <x:c r="A69" s="3">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B69" s="3">
+      <x:c r="B69" s="3" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="C69" s="2" t="s">
@@ -7556,8 +7580,8 @@
       <x:c r="G69" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H69" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H69" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I69" s="56">
         <x:v>46198</x:v>
@@ -7605,7 +7629,7 @@
       <x:c r="A70" s="7">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B70" s="7">
+      <x:c r="B70" s="7" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
@@ -7623,8 +7647,8 @@
       <x:c r="G70" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H70" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H70" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I70" s="55">
         <x:v>46198</x:v>
@@ -7672,7 +7696,7 @@
       <x:c r="A71" s="3">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B71" s="3">
+      <x:c r="B71" s="3" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C71" s="2" t="s">
@@ -7690,8 +7714,8 @@
       <x:c r="G71" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H71" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H71" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I71" s="56">
         <x:v>46198</x:v>
@@ -7739,7 +7763,7 @@
       <x:c r="A72" s="7">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B72" s="7">
+      <x:c r="B72" s="7" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
@@ -7757,8 +7781,8 @@
       <x:c r="G72" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H72" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H72" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I72" s="55">
         <x:v>46198</x:v>
@@ -7806,7 +7830,7 @@
       <x:c r="A73" s="3">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B73" s="3">
+      <x:c r="B73" s="3" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="2" t="s">
@@ -7824,8 +7848,8 @@
       <x:c r="G73" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H73" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H73" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I73" s="56">
         <x:v>46198</x:v>
@@ -7873,7 +7897,7 @@
       <x:c r="A74" s="7">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B74" s="7">
+      <x:c r="B74" s="7" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="C74" s="8" t="s">
@@ -7891,8 +7915,8 @@
       <x:c r="G74" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H74" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H74" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I74" s="55">
         <x:v>46198</x:v>
@@ -7965,7 +7989,7 @@
       <x:c r="A76" s="3">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B76" s="3">
+      <x:c r="B76" s="3" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C76" s="2" t="s">
@@ -7983,8 +8007,8 @@
       <x:c r="G76" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H76" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H76" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I76" s="56">
         <x:v>46198</x:v>
@@ -8032,7 +8056,7 @@
       <x:c r="A77" s="7">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B77" s="7">
+      <x:c r="B77" s="7" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="C77" s="8" t="s">
@@ -8050,8 +8074,8 @@
       <x:c r="G77" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H77" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H77" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I77" s="55">
         <x:v>46198</x:v>
@@ -8099,7 +8123,7 @@
       <x:c r="A78" s="3">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B78" s="3">
+      <x:c r="B78" s="3" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="C78" s="2" t="s">
@@ -8117,8 +8141,8 @@
       <x:c r="G78" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H78" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H78" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I78" s="56">
         <x:v>46198</x:v>
@@ -8166,7 +8190,7 @@
       <x:c r="A79" s="7">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B79" s="7">
+      <x:c r="B79" s="7" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C79" s="8" t="s">
@@ -8184,8 +8208,8 @@
       <x:c r="G79" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H79" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H79" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I79" s="55">
         <x:v>46198</x:v>
@@ -8233,7 +8257,7 @@
       <x:c r="A80" s="3">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B80" s="3">
+      <x:c r="B80" s="3" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C80" s="2" t="s">
@@ -8251,8 +8275,8 @@
       <x:c r="G80" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H80" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H80" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I80" s="56">
         <x:v>46198</x:v>
@@ -8325,7 +8349,7 @@
       <x:c r="A82" s="7">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B82" s="7">
+      <x:c r="B82" s="7" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="C82" s="8" t="s">
@@ -8343,8 +8367,8 @@
       <x:c r="G82" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H82" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H82" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I82" s="55">
         <x:v>46198</x:v>
@@ -8392,7 +8416,7 @@
       <x:c r="A83" s="3">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B83" s="3">
+      <x:c r="B83" s="3" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C83" s="2" t="s">
@@ -8410,8 +8434,8 @@
       <x:c r="G83" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H83" s="3" t="s">
-        <x:v>16</x:v>
+      <x:c r="H83" s="3" t="str">
+        <x:v>Day 02</x:v>
       </x:c>
       <x:c r="I83" s="56">
         <x:v>46197</x:v>
@@ -8459,7 +8483,7 @@
       <x:c r="A84" s="7">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B84" s="7">
+      <x:c r="B84" s="7" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C84" s="8" t="s">
@@ -8477,8 +8501,8 @@
       <x:c r="G84" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H84" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H84" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I84" s="55">
         <x:v>46198</x:v>
@@ -8526,7 +8550,7 @@
       <x:c r="A85" s="3">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B85" s="3">
+      <x:c r="B85" s="3" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
@@ -8544,8 +8568,8 @@
       <x:c r="G85" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H85" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H85" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I85" s="56">
         <x:v>46198</x:v>
@@ -8593,7 +8617,7 @@
       <x:c r="A86" s="7">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B86" s="7">
+      <x:c r="B86" s="7" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C86" s="8" t="s">
@@ -8611,8 +8635,8 @@
       <x:c r="G86" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H86" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H86" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I86" s="55">
         <x:v>46198</x:v>
@@ -8660,7 +8684,7 @@
       <x:c r="A87" s="3">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B87" s="3">
+      <x:c r="B87" s="3" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C87" s="2" t="s">
@@ -8678,8 +8702,8 @@
       <x:c r="G87" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H87" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H87" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I87" s="56">
         <x:v>46198</x:v>
@@ -8727,7 +8751,7 @@
       <x:c r="A88" s="7">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B88" s="7">
+      <x:c r="B88" s="7" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="C88" s="8" t="s">
@@ -8745,8 +8769,8 @@
       <x:c r="G88" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H88" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H88" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I88" s="55">
         <x:v>46198</x:v>
@@ -8819,7 +8843,7 @@
       <x:c r="A90" s="3">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B90" s="3">
+      <x:c r="B90" s="3" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="C90" s="2" t="s">
@@ -8837,8 +8861,8 @@
       <x:c r="G90" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H90" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H90" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I90" s="56">
         <x:v>46198</x:v>
@@ -8886,7 +8910,7 @@
       <x:c r="A91" s="7">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B91" s="7">
+      <x:c r="B91" s="7" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="C91" s="8" t="s">
@@ -8904,8 +8928,8 @@
       <x:c r="G91" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H91" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H91" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I91" s="55">
         <x:v>46198</x:v>
@@ -8953,7 +8977,7 @@
       <x:c r="A92" s="3">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B92" s="3">
+      <x:c r="B92" s="3" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
@@ -8971,8 +8995,8 @@
       <x:c r="G92" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H92" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H92" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I92" s="56">
         <x:v>46198</x:v>
@@ -9020,7 +9044,7 @@
       <x:c r="A93" s="7">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B93" s="7">
+      <x:c r="B93" s="7" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="C93" s="8" t="s">
@@ -9038,8 +9062,8 @@
       <x:c r="G93" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H93" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H93" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I93" s="55">
         <x:v>46198</x:v>
@@ -9087,7 +9111,7 @@
       <x:c r="A94" s="3">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B94" s="3">
+      <x:c r="B94" s="3" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
@@ -9105,8 +9129,8 @@
       <x:c r="G94" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H94" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H94" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I94" s="56">
         <x:v>46198</x:v>
@@ -9154,7 +9178,7 @@
       <x:c r="A95" s="7">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B95" s="7">
+      <x:c r="B95" s="7" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C95" s="8" t="s">
@@ -9172,8 +9196,8 @@
       <x:c r="G95" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H95" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H95" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I95" s="55">
         <x:v>46198</x:v>
@@ -9221,7 +9245,7 @@
       <x:c r="A96" s="3">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B96" s="3">
+      <x:c r="B96" s="3" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="C96" s="2" t="s">
@@ -9239,8 +9263,8 @@
       <x:c r="G96" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H96" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H96" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I96" s="56">
         <x:v>46198</x:v>
@@ -9288,7 +9312,7 @@
       <x:c r="A97" s="7">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B97" s="7">
+      <x:c r="B97" s="7" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="C97" s="8" t="s">
@@ -9306,8 +9330,8 @@
       <x:c r="G97" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H97" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H97" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I97" s="55">
         <x:v>46198</x:v>
@@ -9380,7 +9404,7 @@
       <x:c r="A99" s="3">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B99" s="3">
+      <x:c r="B99" s="3" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="C99" s="2" t="s">
@@ -9398,8 +9422,8 @@
       <x:c r="G99" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H99" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H99" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I99" s="56">
         <x:v>46198</x:v>
@@ -9447,7 +9471,7 @@
       <x:c r="A100" s="7">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B100" s="7">
+      <x:c r="B100" s="7" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="C100" s="8" t="s">
@@ -9465,8 +9489,8 @@
       <x:c r="G100" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H100" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H100" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I100" s="55">
         <x:v>46198</x:v>
@@ -9514,7 +9538,7 @@
       <x:c r="A101" s="3">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B101" s="3">
+      <x:c r="B101" s="3" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="C101" s="2" t="s">
@@ -9532,8 +9556,8 @@
       <x:c r="G101" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H101" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H101" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I101" s="56">
         <x:v>46198</x:v>
@@ -9581,7 +9605,7 @@
       <x:c r="A102" s="7">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B102" s="7">
+      <x:c r="B102" s="7" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="C102" s="8" t="s">
@@ -9599,8 +9623,8 @@
       <x:c r="G102" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H102" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H102" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I102" s="55">
         <x:v>46198</x:v>
@@ -9648,7 +9672,7 @@
       <x:c r="A103" s="3">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B103" s="3">
+      <x:c r="B103" s="3" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="C103" s="2" t="s">
@@ -9666,8 +9690,8 @@
       <x:c r="G103" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H103" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H103" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I103" s="56">
         <x:v>46198</x:v>
@@ -9715,7 +9739,7 @@
       <x:c r="A104" s="7">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B104" s="7">
+      <x:c r="B104" s="7" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="C104" s="8" t="s">
@@ -9733,8 +9757,8 @@
       <x:c r="G104" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H104" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H104" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I104" s="55">
         <x:v>46198</x:v>
@@ -9782,7 +9806,7 @@
       <x:c r="A105" s="3">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B105" s="3">
+      <x:c r="B105" s="3" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="C105" s="2" t="s">
@@ -9800,8 +9824,8 @@
       <x:c r="G105" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H105" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H105" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I105" s="56">
         <x:v>46198</x:v>
@@ -9849,7 +9873,7 @@
       <x:c r="A106" s="7">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B106" s="7">
+      <x:c r="B106" s="7" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="C106" s="8" t="s">
@@ -9867,8 +9891,8 @@
       <x:c r="G106" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H106" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H106" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I106" s="55">
         <x:v>46198</x:v>
@@ -9916,7 +9940,7 @@
       <x:c r="A107" s="3">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B107" s="3">
+      <x:c r="B107" s="3" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="C107" s="2" t="s">
@@ -9934,8 +9958,8 @@
       <x:c r="G107" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H107" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="H107" s="3" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I107" s="56">
         <x:v>46198</x:v>
@@ -9983,7 +10007,7 @@
       <x:c r="A108" s="7">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B108" s="7">
+      <x:c r="B108" s="7" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="C108" s="8" t="s">
@@ -10001,8 +10025,8 @@
       <x:c r="G108" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H108" s="7" t="s">
-        <x:v>19</x:v>
+      <x:c r="H108" s="7" t="str">
+        <x:v>Day 03</x:v>
       </x:c>
       <x:c r="I108" s="55">
         <x:v>46198</x:v>
@@ -10050,7 +10074,7 @@
       <x:c r="A109" s="3">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B109" s="3">
+      <x:c r="B109" s="3" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="C109" s="2" t="s">
@@ -10068,8 +10092,8 @@
       <x:c r="G109" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H109" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H109" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I109" s="56">
         <x:v>46199</x:v>
@@ -10117,7 +10141,7 @@
       <x:c r="A110" s="7">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B110" s="7">
+      <x:c r="B110" s="7" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="C110" s="8" t="s">
@@ -10135,8 +10159,8 @@
       <x:c r="G110" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H110" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H110" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I110" s="55">
         <x:v>46199</x:v>
@@ -10184,7 +10208,7 @@
       <x:c r="A111" s="3">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B111" s="3">
+      <x:c r="B111" s="3" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="C111" s="2" t="s">
@@ -10202,8 +10226,8 @@
       <x:c r="G111" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H111" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H111" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I111" s="56">
         <x:v>46199</x:v>
@@ -10251,7 +10275,7 @@
       <x:c r="A112" s="7">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B112" s="7">
+      <x:c r="B112" s="7" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C112" s="8" t="s">
@@ -10269,8 +10293,8 @@
       <x:c r="G112" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H112" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H112" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I112" s="55">
         <x:v>46199</x:v>
@@ -10318,7 +10342,7 @@
       <x:c r="A113" s="3">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B113" s="3">
+      <x:c r="B113" s="3" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="C113" s="2" t="s">
@@ -10336,8 +10360,8 @@
       <x:c r="G113" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H113" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H113" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I113" s="56">
         <x:v>46199</x:v>
@@ -10385,7 +10409,7 @@
       <x:c r="A114" s="7">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B114" s="7">
+      <x:c r="B114" s="7" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="C114" s="8" t="s">
@@ -10403,8 +10427,8 @@
       <x:c r="G114" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H114" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H114" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I114" s="55">
         <x:v>46199</x:v>
@@ -10452,7 +10476,7 @@
       <x:c r="A115" s="3">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B115" s="3">
+      <x:c r="B115" s="3" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="C115" s="2" t="s">
@@ -10470,8 +10494,8 @@
       <x:c r="G115" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H115" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H115" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I115" s="56">
         <x:v>46199</x:v>
@@ -10519,7 +10543,7 @@
       <x:c r="A116" s="7">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B116" s="7">
+      <x:c r="B116" s="7" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="C116" s="8" t="s">
@@ -10537,8 +10561,8 @@
       <x:c r="G116" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H116" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H116" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I116" s="55">
         <x:v>46199</x:v>
@@ -10611,7 +10635,7 @@
       <x:c r="A118" s="3">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B118" s="3">
+      <x:c r="B118" s="3" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C118" s="2" t="s">
@@ -10629,8 +10653,8 @@
       <x:c r="G118" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H118" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H118" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I118" s="56">
         <x:v>46199</x:v>
@@ -10678,7 +10702,7 @@
       <x:c r="A119" s="7">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B119" s="7">
+      <x:c r="B119" s="7" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="C119" s="8" t="s">
@@ -10696,8 +10720,8 @@
       <x:c r="G119" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H119" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H119" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I119" s="55">
         <x:v>46199</x:v>
@@ -10745,7 +10769,7 @@
       <x:c r="A120" s="3">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B120" s="3">
+      <x:c r="B120" s="3" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="C120" s="2" t="s">
@@ -10763,8 +10787,8 @@
       <x:c r="G120" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H120" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H120" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I120" s="56">
         <x:v>46199</x:v>
@@ -10812,7 +10836,7 @@
       <x:c r="A121" s="7">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B121" s="7">
+      <x:c r="B121" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="C121" s="8" t="s">
@@ -10830,8 +10854,8 @@
       <x:c r="G121" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H121" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H121" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I121" s="55">
         <x:v>46199</x:v>
@@ -10879,7 +10903,7 @@
       <x:c r="A122" s="3">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B122" s="3">
+      <x:c r="B122" s="3" t="n">
         <x:v>143</x:v>
       </x:c>
       <x:c r="C122" s="2" t="s">
@@ -10897,8 +10921,8 @@
       <x:c r="G122" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H122" s="3" t="s">
-        <x:v>30</x:v>
+      <x:c r="H122" s="3" t="str">
+        <x:v>Day 08</x:v>
       </x:c>
       <x:c r="I122" s="56">
         <x:v>46203</x:v>
@@ -10946,7 +10970,7 @@
       <x:c r="A123" s="7">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B123" s="7">
+      <x:c r="B123" s="7" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="C123" s="8" t="s">
@@ -10964,8 +10988,8 @@
       <x:c r="G123" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H123" s="7" t="s">
-        <x:v>32</x:v>
+      <x:c r="H123" s="7" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I123" s="55">
         <x:v>46205</x:v>
@@ -11013,7 +11037,7 @@
       <x:c r="A124" s="3">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B124" s="3">
+      <x:c r="B124" s="3" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="C124" s="2" t="s">
@@ -11031,8 +11055,8 @@
       <x:c r="G124" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H124" s="3" t="s">
-        <x:v>32</x:v>
+      <x:c r="H124" s="3" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I124" s="56">
         <x:v>46205</x:v>
@@ -11080,7 +11104,7 @@
       <x:c r="A125" s="7">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B125" s="7">
+      <x:c r="B125" s="7" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="C125" s="8" t="s">
@@ -11098,8 +11122,8 @@
       <x:c r="G125" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H125" s="7" t="s">
-        <x:v>32</x:v>
+      <x:c r="H125" s="7" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I125" s="55">
         <x:v>46205</x:v>
@@ -11172,7 +11196,7 @@
       <x:c r="A127" s="3">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B127" s="3">
+      <x:c r="B127" s="3" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="C127" s="2" t="s">
@@ -11190,8 +11214,8 @@
       <x:c r="G127" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H127" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H127" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I127" s="56">
         <x:v>46199</x:v>
@@ -11239,7 +11263,7 @@
       <x:c r="A128" s="7">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B128" s="7">
+      <x:c r="B128" s="7" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C128" s="8" t="s">
@@ -11257,8 +11281,8 @@
       <x:c r="G128" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H128" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H128" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I128" s="55">
         <x:v>46199</x:v>
@@ -11306,7 +11330,7 @@
       <x:c r="A129" s="3">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B129" s="3">
+      <x:c r="B129" s="3" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="C129" s="2" t="s">
@@ -11324,8 +11348,8 @@
       <x:c r="G129" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H129" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H129" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I129" s="56">
         <x:v>46199</x:v>
@@ -11373,7 +11397,7 @@
       <x:c r="A130" s="7">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B130" s="7">
+      <x:c r="B130" s="7" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="C130" s="8" t="s">
@@ -11391,8 +11415,8 @@
       <x:c r="G130" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H130" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H130" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I130" s="55">
         <x:v>46199</x:v>
@@ -11440,7 +11464,7 @@
       <x:c r="A131" s="3">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B131" s="3">
+      <x:c r="B131" s="3" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="C131" s="2" t="s">
@@ -11458,8 +11482,8 @@
       <x:c r="G131" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H131" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H131" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I131" s="56">
         <x:v>46199</x:v>
@@ -11507,7 +11531,7 @@
       <x:c r="A132" s="7">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B132" s="7">
+      <x:c r="B132" s="7" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="C132" s="8" t="s">
@@ -11525,8 +11549,8 @@
       <x:c r="G132" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H132" s="7" t="s">
-        <x:v>21</x:v>
+      <x:c r="H132" s="7" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I132" s="55">
         <x:v>46199</x:v>
@@ -11574,7 +11598,7 @@
       <x:c r="A133" s="3">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B133" s="3">
+      <x:c r="B133" s="3" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="C133" s="2" t="s">
@@ -11592,8 +11616,8 @@
       <x:c r="G133" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H133" s="3" t="s">
-        <x:v>21</x:v>
+      <x:c r="H133" s="3" t="str">
+        <x:v>Day 04</x:v>
       </x:c>
       <x:c r="I133" s="56">
         <x:v>46199</x:v>
@@ -11641,7 +11665,7 @@
       <x:c r="A134" s="7">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B134" s="7">
+      <x:c r="B134" s="7" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="C134" s="8" t="s">
@@ -11659,8 +11683,8 @@
       <x:c r="G134" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H134" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H134" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I134" s="55">
         <x:v>46200</x:v>
@@ -11708,7 +11732,7 @@
       <x:c r="A135" s="3">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B135" s="3">
+      <x:c r="B135" s="3" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="C135" s="2" t="s">
@@ -11726,8 +11750,8 @@
       <x:c r="G135" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H135" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H135" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I135" s="56">
         <x:v>46200</x:v>
@@ -11817,7 +11841,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H137" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I137" s="55"/>
       <x:c r="J137" s="7"/>
@@ -11845,7 +11869,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U137" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="34.04999923706055" customHeight="1">
@@ -11869,7 +11893,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H138" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I138" s="56"/>
       <x:c r="J138" s="3"/>
@@ -11897,7 +11921,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U138" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="34.04999923706055" customHeight="1">
@@ -11921,7 +11945,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H139" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I139" s="55"/>
       <x:c r="J139" s="7"/>
@@ -11949,7 +11973,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U139" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="22.049999237060547" customHeight="1">
@@ -11981,7 +12005,7 @@
       <x:c r="A141" s="3">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B141" s="3">
+      <x:c r="B141" s="3" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="C141" s="2" t="s">
@@ -11999,8 +12023,8 @@
       <x:c r="G141" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H141" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H141" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I141" s="56">
         <x:v>46200</x:v>
@@ -12048,7 +12072,7 @@
       <x:c r="A142" s="7">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B142" s="7">
+      <x:c r="B142" s="7" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="C142" s="8" t="s">
@@ -12066,8 +12090,8 @@
       <x:c r="G142" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H142" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H142" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I142" s="55">
         <x:v>46200</x:v>
@@ -12115,7 +12139,7 @@
       <x:c r="A143" s="3">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B143" s="3">
+      <x:c r="B143" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="C143" s="2" t="s">
@@ -12133,8 +12157,8 @@
       <x:c r="G143" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H143" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H143" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I143" s="56">
         <x:v>46200</x:v>
@@ -12182,7 +12206,7 @@
       <x:c r="A144" s="7">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B144" s="7">
+      <x:c r="B144" s="7" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="C144" s="8" t="s">
@@ -12200,8 +12224,8 @@
       <x:c r="G144" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H144" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H144" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I144" s="55">
         <x:v>46200</x:v>
@@ -12249,7 +12273,7 @@
       <x:c r="A145" s="3">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B145" s="3">
+      <x:c r="B145" s="3" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="C145" s="2" t="s">
@@ -12267,8 +12291,8 @@
       <x:c r="G145" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H145" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H145" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I145" s="56">
         <x:v>46200</x:v>
@@ -12316,7 +12340,7 @@
       <x:c r="A146" s="7">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B146" s="7">
+      <x:c r="B146" s="7" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="C146" s="8" t="s">
@@ -12334,8 +12358,8 @@
       <x:c r="G146" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H146" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H146" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I146" s="55">
         <x:v>46200</x:v>
@@ -12383,7 +12407,7 @@
       <x:c r="A147" s="3">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B147" s="3">
+      <x:c r="B147" s="3" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="C147" s="2" t="s">
@@ -12401,8 +12425,8 @@
       <x:c r="G147" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H147" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H147" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I147" s="56">
         <x:v>46200</x:v>
@@ -12450,7 +12474,7 @@
       <x:c r="A148" s="7">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B148" s="7">
+      <x:c r="B148" s="7" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="C148" s="8" t="s">
@@ -12468,8 +12492,8 @@
       <x:c r="G148" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H148" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H148" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I148" s="55">
         <x:v>46200</x:v>
@@ -12517,7 +12541,7 @@
       <x:c r="A149" s="3">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B149" s="3">
+      <x:c r="B149" s="3" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="C149" s="2" t="s">
@@ -12535,8 +12559,8 @@
       <x:c r="G149" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H149" s="3" t="s">
-        <x:v>23</x:v>
+      <x:c r="H149" s="3" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I149" s="56">
         <x:v>46200</x:v>
@@ -12584,7 +12608,7 @@
       <x:c r="A150" s="7">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B150" s="7">
+      <x:c r="B150" s="7" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="C150" s="8" t="s">
@@ -12602,8 +12626,8 @@
       <x:c r="G150" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H150" s="7" t="s">
-        <x:v>23</x:v>
+      <x:c r="H150" s="7" t="str">
+        <x:v>Day 05</x:v>
       </x:c>
       <x:c r="I150" s="55">
         <x:v>46200</x:v>
@@ -12651,9 +12675,7 @@
       <x:c r="A151" s="3">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B151" s="3">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="B151" s="3"/>
       <x:c r="C151" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -12670,7 +12692,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H151" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I151" s="56"/>
       <x:c r="J151" s="3"/>
@@ -12706,7 +12728,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="U151" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="34.04999923706055" customHeight="1">
@@ -12730,7 +12752,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H152" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I152" s="55"/>
       <x:c r="J152" s="7"/>
@@ -12758,7 +12780,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U152" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="34.04999923706055" customHeight="1">
@@ -12782,7 +12804,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H153" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I153" s="56"/>
       <x:c r="J153" s="3"/>
@@ -12810,7 +12832,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U153" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="34.04999923706055" customHeight="1">
@@ -12834,7 +12856,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H154" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I154" s="55"/>
       <x:c r="J154" s="7"/>
@@ -12862,7 +12884,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U154" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="34.04999923706055" customHeight="1">
@@ -12886,7 +12908,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H155" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I155" s="56"/>
       <x:c r="J155" s="3"/>
@@ -12914,7 +12936,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U155" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="34.04999923706055" customHeight="1">
@@ -12938,7 +12960,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H156" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I156" s="55"/>
       <x:c r="J156" s="7"/>
@@ -12966,7 +12988,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U156" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="34.04999923706055" customHeight="1">
@@ -12990,7 +13012,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H157" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I157" s="56"/>
       <x:c r="J157" s="3"/>
@@ -13018,7 +13040,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U157" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="34.04999923706055" customHeight="1">
@@ -13042,7 +13064,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H158" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I158" s="55"/>
       <x:c r="J158" s="7"/>
@@ -13070,7 +13092,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U158" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="34.04999923706055" customHeight="1">
@@ -13094,7 +13116,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H159" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I159" s="56"/>
       <x:c r="J159" s="3"/>
@@ -13122,7 +13144,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U159" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="34.04999923706055" customHeight="1">
@@ -13146,7 +13168,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H160" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I160" s="55"/>
       <x:c r="J160" s="7"/>
@@ -13174,14 +13196,14 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U160" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="34.04999923706055" customHeight="1">
       <x:c r="A161" s="3">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B161" s="3">
+      <x:c r="B161" s="3" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="C161" s="2" t="s">
@@ -13199,8 +13221,8 @@
       <x:c r="G161" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H161" s="3" t="s">
-        <x:v>27</x:v>
+      <x:c r="H161" s="3" t="str">
+        <x:v>Day 07</x:v>
       </x:c>
       <x:c r="I161" s="56">
         <x:v>46202</x:v>
@@ -13265,7 +13287,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H162" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I162" s="55"/>
       <x:c r="J162" s="7"/>
@@ -13293,7 +13315,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U162" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="34.04999923706055" customHeight="1">
@@ -13317,7 +13339,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H163" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I163" s="56"/>
       <x:c r="J163" s="3"/>
@@ -13345,7 +13367,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U163" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="34.04999923706055" customHeight="1">
@@ -13576,7 +13598,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H167" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I167" s="56"/>
       <x:c r="J167" s="3"/>
@@ -13604,7 +13626,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U167" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="34.04999923706055" customHeight="1">
@@ -13697,7 +13719,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H169" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I169" s="56"/>
       <x:c r="J169" s="3"/>
@@ -13725,7 +13747,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U169" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="34.04999923706055" customHeight="1">
@@ -13749,7 +13771,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H170" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I170" s="55"/>
       <x:c r="J170" s="7"/>
@@ -13777,7 +13799,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U170" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="34.04999923706055" customHeight="1">
@@ -13801,7 +13823,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H171" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I171" s="56"/>
       <x:c r="J171" s="3"/>
@@ -13829,7 +13851,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U171" s="2" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="34.04999923706055" customHeight="1">
@@ -13853,7 +13875,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H172" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I172" s="55"/>
       <x:c r="J172" s="7"/>
@@ -13889,14 +13911,14 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="U172" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="34.04999923706055" customHeight="1">
       <x:c r="A173" s="3">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B173" s="3">
+      <x:c r="B173" s="3" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="C173" s="2" t="s">
@@ -13914,8 +13936,8 @@
       <x:c r="G173" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H173" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H173" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I173" s="56">
         <x:v>46201</x:v>
@@ -13988,7 +14010,7 @@
       <x:c r="A175" s="7">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B175" s="7">
+      <x:c r="B175" s="7" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="C175" s="8" t="s">
@@ -14006,8 +14028,8 @@
       <x:c r="G175" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H175" s="7" t="s">
-        <x:v>32</x:v>
+      <x:c r="H175" s="7" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I175" s="55">
         <x:v>46205</x:v>
@@ -14055,7 +14077,7 @@
       <x:c r="A176" s="3">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B176" s="3">
+      <x:c r="B176" s="3" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="C176" s="2" t="s">
@@ -14073,8 +14095,8 @@
       <x:c r="G176" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H176" s="3" t="s">
-        <x:v>32</x:v>
+      <x:c r="H176" s="3" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I176" s="56">
         <x:v>46205</x:v>
@@ -14122,7 +14144,7 @@
       <x:c r="A177" s="7">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B177" s="7">
+      <x:c r="B177" s="7" t="n">
         <x:v>149</x:v>
       </x:c>
       <x:c r="C177" s="8" t="s">
@@ -14140,8 +14162,8 @@
       <x:c r="G177" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H177" s="7" t="s">
-        <x:v>32</x:v>
+      <x:c r="H177" s="7" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I177" s="55">
         <x:v>46205</x:v>
@@ -14189,7 +14211,7 @@
       <x:c r="A178" s="3">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B178" s="3">
+      <x:c r="B178" s="3" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="C178" s="2" t="s">
@@ -14207,8 +14229,8 @@
       <x:c r="G178" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H178" s="3" t="s">
-        <x:v>32</x:v>
+      <x:c r="H178" s="3" t="str">
+        <x:v>Day 09</x:v>
       </x:c>
       <x:c r="I178" s="56">
         <x:v>46205</x:v>
@@ -14407,7 +14429,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="H181" s="57" t="str">
-        <x:v>Day 11</x:v>
+        <x:v>Day 12</x:v>
       </x:c>
       <x:c r="I181" s="55"/>
       <x:c r="J181" s="7"/>
@@ -14435,7 +14457,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="U181" s="8" t="str">
-        <x:v>Planned for 2026-07-04. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="25.049999237060547" customHeight="1">
@@ -14492,7 +14514,7 @@
       <x:c r="A184" s="3">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="B184" s="3">
+      <x:c r="B184" s="3" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="C184" s="2" t="s">
@@ -14510,8 +14532,8 @@
       <x:c r="G184" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H184" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H184" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I184" s="56">
         <x:v>46201</x:v>
@@ -14559,7 +14581,7 @@
       <x:c r="A185" s="7">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B185" s="7">
+      <x:c r="B185" s="7" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="C185" s="8" t="s">
@@ -14577,8 +14599,8 @@
       <x:c r="G185" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H185" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H185" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I185" s="55">
         <x:v>46201</x:v>
@@ -14626,7 +14648,7 @@
       <x:c r="A186" s="3">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B186" s="3">
+      <x:c r="B186" s="3" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="C186" s="2" t="s">
@@ -14644,8 +14666,8 @@
       <x:c r="G186" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H186" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H186" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I186" s="56">
         <x:v>46201</x:v>
@@ -14693,7 +14715,7 @@
       <x:c r="A187" s="7">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B187" s="7">
+      <x:c r="B187" s="7" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="C187" s="8" t="s">
@@ -14711,8 +14733,8 @@
       <x:c r="G187" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H187" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H187" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I187" s="55">
         <x:v>46201</x:v>
@@ -14760,7 +14782,7 @@
       <x:c r="A188" s="3">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B188" s="3">
+      <x:c r="B188" s="3" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="C188" s="2" t="s">
@@ -14778,8 +14800,8 @@
       <x:c r="G188" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H188" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H188" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I188" s="56">
         <x:v>46201</x:v>
@@ -14852,7 +14874,7 @@
       <x:c r="A190" s="7">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B190" s="7">
+      <x:c r="B190" s="7" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="C190" s="8" t="s">
@@ -14870,8 +14892,8 @@
       <x:c r="G190" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H190" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H190" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I190" s="55">
         <x:v>46201</x:v>
@@ -14919,7 +14941,7 @@
       <x:c r="A191" s="3">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B191" s="3">
+      <x:c r="B191" s="3" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="C191" s="2" t="s">
@@ -14937,8 +14959,8 @@
       <x:c r="G191" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H191" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H191" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I191" s="56">
         <x:v>46201</x:v>
@@ -14986,7 +15008,7 @@
       <x:c r="A192" s="7">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B192" s="7">
+      <x:c r="B192" s="7" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="C192" s="8" t="s">
@@ -15004,8 +15026,8 @@
       <x:c r="G192" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H192" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H192" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I192" s="55">
         <x:v>46201</x:v>
@@ -15053,7 +15075,7 @@
       <x:c r="A193" s="3">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B193" s="3">
+      <x:c r="B193" s="3" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="C193" s="2" t="s">
@@ -15071,8 +15093,8 @@
       <x:c r="G193" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H193" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H193" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I193" s="56">
         <x:v>46201</x:v>
@@ -15120,7 +15142,7 @@
       <x:c r="A194" s="7">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B194" s="7">
+      <x:c r="B194" s="7" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="C194" s="8" t="s">
@@ -15138,8 +15160,8 @@
       <x:c r="G194" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H194" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H194" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I194" s="55">
         <x:v>46201</x:v>
@@ -15187,7 +15209,7 @@
       <x:c r="A195" s="3">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B195" s="3">
+      <x:c r="B195" s="3" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="C195" s="2" t="s">
@@ -15205,8 +15227,8 @@
       <x:c r="G195" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H195" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H195" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I195" s="56">
         <x:v>46201</x:v>
@@ -15254,7 +15276,7 @@
       <x:c r="A196" s="7">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B196" s="7">
+      <x:c r="B196" s="7" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="C196" s="8" t="s">
@@ -15272,8 +15294,8 @@
       <x:c r="G196" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H196" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H196" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I196" s="55">
         <x:v>46201</x:v>
@@ -15321,7 +15343,7 @@
       <x:c r="A197" s="3">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B197" s="3">
+      <x:c r="B197" s="3" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="C197" s="2" t="s">
@@ -15339,8 +15361,8 @@
       <x:c r="G197" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H197" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H197" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I197" s="56">
         <x:v>46201</x:v>
@@ -15388,7 +15410,7 @@
       <x:c r="A198" s="7">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B198" s="7">
+      <x:c r="B198" s="7" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="C198" s="8" t="s">
@@ -15406,8 +15428,8 @@
       <x:c r="G198" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H198" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H198" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I198" s="55">
         <x:v>46201</x:v>
@@ -15455,7 +15477,7 @@
       <x:c r="A199" s="3">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="B199" s="3">
+      <x:c r="B199" s="3" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="C199" s="2" t="s">
@@ -15473,8 +15495,8 @@
       <x:c r="G199" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H199" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H199" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I199" s="56">
         <x:v>46201</x:v>
@@ -15547,7 +15569,7 @@
       <x:c r="A201" s="7">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="B201" s="7">
+      <x:c r="B201" s="7" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="C201" s="8" t="s">
@@ -15563,8 +15585,8 @@
       <x:c r="G201" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H201" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H201" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I201" s="55">
         <x:v>46201</x:v>
@@ -15612,7 +15634,7 @@
       <x:c r="A202" s="3">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B202" s="3">
+      <x:c r="B202" s="3" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="C202" s="2" t="s">
@@ -15628,8 +15650,8 @@
       <x:c r="G202" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H202" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H202" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I202" s="56">
         <x:v>46201</x:v>
@@ -15677,7 +15699,7 @@
       <x:c r="A203" s="7">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B203" s="7">
+      <x:c r="B203" s="7" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="C203" s="8" t="s">
@@ -15693,8 +15715,8 @@
       <x:c r="G203" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H203" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="H203" s="7" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I203" s="55">
         <x:v>46201</x:v>
@@ -15742,7 +15764,7 @@
       <x:c r="A204" s="3">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="B204" s="3">
+      <x:c r="B204" s="3" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="C204" s="2" t="s">
@@ -15758,8 +15780,8 @@
       <x:c r="G204" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H204" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="H204" s="3" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I204" s="56">
         <x:v>46201</x:v>
@@ -15807,7 +15829,7 @@
       <x:c r="A205" s="12">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B205" s="12">
+      <x:c r="B205" s="12" t="n">
         <x:v>141</x:v>
       </x:c>
       <x:c r="C205" s="13" t="s">
@@ -15823,8 +15845,8 @@
       <x:c r="G205" s="12" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H205" s="12" t="s">
-        <x:v>25</x:v>
+      <x:c r="H205" s="12" t="str">
+        <x:v>Day 06</x:v>
       </x:c>
       <x:c r="I205" s="61">
         <x:v>46201</x:v>

--- a/HDLBits_Tracker.xlsx
+++ b/HDLBits_Tracker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb227a53ac6834bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="Rde6eb7f34cc24e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd6d647ce0b284e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="R540d103a86d247a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,9 +26,6 @@
     <x:t xml:space="preserve">Full series</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Current review</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Sequence audit: 178/178 HDLBits IDs match the live website order (CS450 excluded).</x:t>
   </x:si>
   <x:si>
@@ -1583,30 +1580,6 @@
     <x:t xml:space="preserve">SUBSECTION · Sequential Logic → More Circuits</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Rule 90</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rule90</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">To Do</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not attempted yet. Read the HDLBits question, design the circuit or testbench, and obtain a successful submission.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rule 110</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rule110</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Conway's Game of Life 16x16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">conwaylife</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">SUBSECTION · Sequential Logic → Finite State Machines</x:t>
   </x:si>
   <x:si>
@@ -1736,9 +1709,6 @@
     <x:t xml:space="preserve">lemmings2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Attempted but not yet solved. Review the latest captured draft, trace state transitions, and resubmit after correcting the falling-state logic.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Lemmings 3</x:t>
   </x:si>
   <x:si>
@@ -1805,18 +1775,6 @@
     <x:t xml:space="preserve">Three-state Mealy detector for overlapping 101 with active-low asynchronous reset. State S10 plus input 1 asserts z in the detection cycle.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Q5a: Serial two's complementer (Moore FSM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/ece241_2014_q5a</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q5b: Serial two's complementer (Mealy FSM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/ece241_2014_q5b</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Q3a: FSM</x:t>
   </x:si>
   <x:si>
@@ -1835,40 +1793,10 @@
     <x:t xml:space="preserve">exams/2014_q3c</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Q6b: FSM next-state logic</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/m2014_q6b</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Q6c: FSM one-hot next-state logic</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">exams/m2014_q6c</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q6: FSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/m2014_q6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q2a: FSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/2012_q2fsm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q2b: One-hot FSM equations</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/2012_q2b</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/2013_q2afsm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Attempted but not yet solved. Review the arbiter state diagram, request priority rules, and grant-hold behavior before resubmitting.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Q2b: Another FSM</x:t>
@@ -1932,12 +1860,6 @@
 shift_ena is a Moore-style combinational decode of the registered count. It is high for count values 0, 1, 2, and 3, giving exactly four complete clock intervals, and becomes low when the fourth post-reset edge changes the count to 4. Saturation prevents the counter from wrapping back to zero and accidentally reasserting the enable after eight cycles.
 Reset timing matters. Because reset is synchronous, asserting it between clock edges does not immediately modify count or the output. The next rising edge loads zero, after which the output is high and the four-cycle window starts again. No explicit else count &lt;= count assignment is needed in clocked logic: when no branch assigns the register, the flip-flops retain their previous value.
 **Cycle trace:** reset edge→0/high, then successive edges produce 1/high, 2/high, 3/high, 4/low, followed by 4/low indefinitely until another reset edge.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FSM: One-hot logic equations</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">exams/review2015_fsmonehot</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SECTION · Verification: Reading Simulations</x:t>
@@ -2184,10 +2106,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="0%"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="16">
     <x:font>
@@ -2281,7 +2206,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2363,8 +2288,48 @@
         <x:fgColor rgb="FFFFFF99"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E1F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF99"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E1F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF99"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -2420,12 +2385,26 @@
         <x:color rgb="FFA6BCE6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFAFC5E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAFC5E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAFC5E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAFC5E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="79">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2625,6 +2604,63 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Hyperlink" xfId="1"/>
@@ -2931,8 +2967,7 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="31" t="str">
-        <x:f>"Exact website sequence · "&amp;A6&amp;" of "&amp;D6&amp;" completed · "&amp;B6&amp;" review · "&amp;C6&amp;" to do</x:f>
-        <x:v>Exact website sequence · 157 of 178 completed · 2 review · 19 to do</x:v>
+        <x:v>Exact website sequence · 178 of 178 completed · 0 review · 0 to do</x:v>
       </x:c>
       <x:c r="B3" s="31"/>
       <x:c r="C3" s="31"/>
@@ -2956,37 +2991,33 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="33" t="str">
-        <x:v>Day 12 plan</x:v>
-      </x:c>
-      <x:c r="G5" s="33" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="33" t="s">
-        <x:v>5</x:v>
+        <x:v>Day 14 status</x:v>
+      </x:c>
+      <x:c r="G5" s="33" t="str">
+        <x:v>Live profile</x:v>
+      </x:c>
+      <x:c r="H5" s="33" t="str">
+        <x:v>Live profile</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28.049999237060547" customHeight="1">
       <x:c r="A6" s="18" t="n">
-        <x:f>COUNTIF('Tracker'!$G$6:$G$205,"Completed")</x:f>
-        <x:v>157</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B6" s="18" t="n">
-        <x:f>COUNTIF('Tracker'!$G$6:$G$205,"Review")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
-        <x:f>COUNTIF('Tracker'!$G$6:$G$205,"To Do")</x:f>
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="18" t="n">
-        <x:f>COUNTA('Tracker'!$F$6:$F$205)</x:f>
         <x:v>178</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
         <x:v>Date</x:v>
       </x:c>
       <x:c r="G6" s="62" t="n">
-        <x:v>46208</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="H6" s="34"/>
     </x:row>
@@ -2995,13 +3026,13 @@
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="G7" s="34" t="str">
-        <x:v>21 questions · 19 To Do + 2 Review</x:v>
+        <x:v>0 questions · 0 To Do + 0 Review</x:v>
       </x:c>
       <x:c r="H7" s="34"/>
     </x:row>
     <x:row r="8" ht="25.049999237060547" customHeight="1">
       <x:c r="A8" s="32" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="32"/>
       <x:c r="C8" s="32"/>
@@ -3010,36 +3041,36 @@
         <x:v>Queue</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
-        <x:v>study/Day 12.md</x:v>
+        <x:v>study/Review.md</x:v>
       </x:c>
       <x:c r="H8" s="35"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="19" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="s">
+      <x:c r="C10" s="19" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="19" t="s">
+      <x:c r="E10" s="19" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="s">
+      <x:c r="F10" s="19" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F10" s="19" t="s">
+      <x:c r="G10" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="19" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="19" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B11" s="65">
         <x:v>46196</x:v>
@@ -3049,10 +3080,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E11" s="25" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="24" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E11,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3065,7 +3096,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="65">
         <x:v>46197</x:v>
@@ -3075,10 +3106,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="25" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="24" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E12,'Tracker'!$D$6:$D$205,F12,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3091,7 +3122,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="65">
         <x:v>46198</x:v>
@@ -3101,10 +3132,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="25" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F13" s="24" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E13,'Tracker'!$D$6:$D$205,F13,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3117,7 +3148,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="65">
         <x:v>46199</x:v>
@@ -3127,10 +3158,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E14" s="25" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F14" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G14" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E14,'Tracker'!$D$6:$D$205,F14,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3143,7 +3174,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="65">
         <x:v>46200</x:v>
@@ -3153,10 +3184,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E15" s="25" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="24" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G15" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E15,'Tracker'!$D$6:$D$205,F15,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3169,7 +3200,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="65">
         <x:v>46201</x:v>
@@ -3179,10 +3210,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E16" s="25" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F16" s="24" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G16" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E16,'Tracker'!$D$6:$D$205,F16,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3195,7 +3226,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="27" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B17" s="66">
         <x:v>46202</x:v>
@@ -3205,10 +3236,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="F17" s="24" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="G17" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E17,'Tracker'!$D$6:$D$205,F17,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3221,7 +3252,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="27" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="66">
         <x:v>46203</x:v>
@@ -3231,10 +3262,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F18" s="24" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E18,'Tracker'!$D$6:$D$205,F18,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3247,7 +3278,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="27" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="66">
         <x:v>46205</x:v>
@@ -3257,10 +3288,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E19" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F19" s="24" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G19" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E19,'Tracker'!$D$6:$D$205,F19,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3283,10 +3314,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E20" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F20" s="24" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G20" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E20,'Tracker'!$D$6:$D$205,F20,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3306,13 +3337,13 @@
       </x:c>
       <x:c r="C21" s="73" t="n">
         <x:f>COUNTIFS('Tracker'!$H$6:$H$205,A21,'Tracker'!$G$6:$G$205,"Completed")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E21" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F21" s="24" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G21" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E21,'Tracker'!$D$6:$D$205,F21,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3331,13 +3362,14 @@
         <x:v>46208</x:v>
       </x:c>
       <x:c r="C22" s="78" t="n">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS('Tracker'!$H$6:$H$205,A22,'Tracker'!$G$6:$G$205,"Completed")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="24" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G22" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E22,'Tracker'!$D$6:$D$205,F22,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3349,11 +3381,21 @@
       </x:c>
     </x:row>
     <x:row r="23">
+      <x:c r="A23" s="82" t="str">
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="B23" s="84" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="C23" s="87" t="n">
+        <x:f>COUNTIFS('Tracker'!$H$6:$H$205,A23,'Tracker'!$G$6:$G$205,"Completed")</x:f>
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="E23" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="24" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G23" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E23,'Tracker'!$D$6:$D$205,F23,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3365,31 +3407,38 @@
       </x:c>
     </x:row>
     <x:row r="24">
+      <x:c r="A24" s="101" t="str">
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="B24" s="104" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="C24" s="105" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="E24" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="24" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G24" s="26" t="n">
-        <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E24,'Tracker'!$D$6:$D$205,F24,'Tracker'!$G$6:$G$205,"Completed")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H24" s="26" t="n">
-        <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E24,'Tracker'!$D$6:$D$205,F24)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="E25" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="24" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G25" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E25,'Tracker'!$D$6:$D$205,F25,'Tracker'!$G$6:$G$205,"Completed")</x:f>
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H25" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E25,'Tracker'!$D$6:$D$205,F25)</x:f>
@@ -3398,26 +3447,24 @@
     </x:row>
     <x:row r="26">
       <x:c r="E26" s="25" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="24" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G26" s="26" t="n">
-        <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E26,'Tracker'!$D$6:$D$205,F26,'Tracker'!$G$6:$G$205,"Completed")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H26" s="26" t="n">
-        <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E26,'Tracker'!$D$6:$D$205,F26)</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="E27" s="25" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F27" s="24" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F27" s="24" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="G27" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E27,'Tracker'!$D$6:$D$205,F27,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3430,10 +3477,10 @@
     </x:row>
     <x:row r="28">
       <x:c r="E28" s="25" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F28" s="24" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G28" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E28,'Tracker'!$D$6:$D$205,F28,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3446,10 +3493,10 @@
     </x:row>
     <x:row r="29">
       <x:c r="E29" s="25" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F29" s="24" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="26" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$205,E29,'Tracker'!$G$6:$G$205,"Completed")</x:f>
@@ -3500,138 +3547,137 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="P1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="T1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U1" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="P2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="T2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22.950000762939453" customHeight="1">
       <x:c r="A3" s="37" t="str">
-        <x:f>"Website sequence verified: "&amp;'Summary'!$D$6&amp;" of "&amp;'Summary'!$D$6&amp;" IDs in exact order · "&amp;'Summary'!$A$6&amp;" completed · "&amp;'Summary'!$B$6&amp;" review · "&amp;'Summary'!$C$6&amp;" to do</x:f>
-        <x:v>Website sequence verified: 178 of 178 IDs in exact order · 157 completed · 2 review · 19 to do</x:v>
+        <x:v>Website sequence verified: 178 of 178 IDs in exact order · 178 completed · 0 review · 0 to do</x:v>
       </x:c>
       <x:c r="B3" s="37"/>
       <x:c r="C3" s="37"/>
@@ -3656,72 +3702,72 @@
     </x:row>
     <x:row r="5" ht="37.95000076293945" customHeight="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="C5" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
+      <x:c r="G5" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
+      <x:c r="J5" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J5" s="1" t="s">
+      <x:c r="K5" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K5" s="1" t="s">
+      <x:c r="L5" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="L5" s="1" t="s">
+      <x:c r="M5" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="M5" s="1" t="s">
+      <x:c r="N5" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="N5" s="1" t="s">
+      <x:c r="O5" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="O5" s="1" t="s">
+      <x:c r="P5" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="P5" s="1" t="s">
+      <x:c r="Q5" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="Q5" s="1" t="s">
+      <x:c r="R5" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="R5" s="1" t="s">
+      <x:c r="S5" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="S5" s="1" t="s">
+      <x:c r="T5" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="T5" s="1" t="s">
+      <x:c r="U5" s="1" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="U5" s="1" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.049999237060547" customHeight="1">
       <x:c r="A6" s="38" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="38"/>
       <x:c r="C6" s="38"/>
@@ -3876,7 +3922,7 @@
     </x:row>
     <x:row r="9" ht="25.049999237060547" customHeight="1">
       <x:c r="A9" s="41" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="41"/>
       <x:c r="C9" s="41"/>
@@ -3901,7 +3947,7 @@
     </x:row>
     <x:row r="10" ht="22.049999237060547" customHeight="1">
       <x:c r="A10" s="44" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B10" s="44"/>
       <x:c r="C10" s="44"/>
@@ -3932,16 +3978,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E11" s="2" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
         <x:v>1</x:v>
@@ -3953,7 +3999,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K11" s="3">
         <x:v>1</x:v>
@@ -3987,7 +4033,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T11" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U11" s="2"/>
     </x:row>
@@ -3999,16 +4045,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E12" s="8" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="G12" s="7" t="s">
         <x:v>1</x:v>
@@ -4020,7 +4066,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K12" s="7">
         <x:v>2</x:v>
@@ -4054,7 +4100,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T12" s="8" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="U12" s="8"/>
     </x:row>
@@ -4066,16 +4112,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E13" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="F13" s="2" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
         <x:v>1</x:v>
@@ -4087,7 +4133,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K13" s="3">
         <x:v>1</x:v>
@@ -4121,7 +4167,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/notgate, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T13" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="U13" s="2"/>
     </x:row>
@@ -4133,16 +4179,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D14" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E14" s="8" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="G14" s="7" t="s">
         <x:v>1</x:v>
@@ -4154,7 +4200,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J14" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K14" s="7">
         <x:v>1</x:v>
@@ -4188,7 +4234,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/andgate, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T14" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="U14" s="8"/>
     </x:row>
@@ -4200,16 +4246,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D15" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E15" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F15" s="2" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="F15" s="2" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
         <x:v>1</x:v>
@@ -4221,7 +4267,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K15" s="3">
         <x:v>6</x:v>
@@ -4255,7 +4301,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/norgate, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T15" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="U15" s="2"/>
     </x:row>
@@ -4267,16 +4313,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D16" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E16" s="8" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="G16" s="7" t="s">
         <x:v>1</x:v>
@@ -4288,7 +4334,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J16" s="7" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K16" s="7">
         <x:v>2</x:v>
@@ -4322,7 +4368,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/xnorgate, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T16" s="8" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="U16" s="8"/>
     </x:row>
@@ -4334,16 +4380,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D17" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E17" s="2" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F17" s="2" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="F17" s="2" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
         <x:v>1</x:v>
@@ -4355,7 +4401,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K17" s="3">
         <x:v>1</x:v>
@@ -4389,7 +4435,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire_decl, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T17" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="U17" s="2"/>
     </x:row>
@@ -4401,16 +4447,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D18" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E18" s="8" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="G18" s="7" t="s">
         <x:v>1</x:v>
@@ -4422,7 +4468,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J18" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K18" s="7">
         <x:v>1</x:v>
@@ -4456,13 +4502,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7458, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T18" s="8" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="U18" s="8"/>
     </x:row>
     <x:row r="19" ht="22.049999237060547" customHeight="1">
       <x:c r="A19" s="44" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B19" s="44"/>
       <x:c r="C19" s="44"/>
@@ -4493,16 +4539,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
         <x:v>1</x:v>
@@ -4514,7 +4560,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K20" s="3">
         <x:v>1</x:v>
@@ -4548,7 +4594,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector0, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T20" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="U20" s="2"/>
     </x:row>
@@ -4560,16 +4606,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D21" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="F21" s="8" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="G21" s="7" t="s">
         <x:v>1</x:v>
@@ -4581,7 +4627,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J21" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K21" s="7">
         <x:v>10</x:v>
@@ -4615,7 +4661,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T21" s="8" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="U21" s="8"/>
     </x:row>
@@ -4627,16 +4673,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F22" s="2" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="F22" s="2" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
         <x:v>1</x:v>
@@ -4648,7 +4694,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K22" s="3">
         <x:v>3</x:v>
@@ -4682,7 +4728,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T22" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="U22" s="2"/>
     </x:row>
@@ -4694,16 +4740,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D23" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E23" s="8" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="F23" s="8" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="G23" s="7" t="s">
         <x:v>1</x:v>
@@ -4715,7 +4761,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J23" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K23" s="7">
         <x:v>1</x:v>
@@ -4749,7 +4795,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorgates, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T23" s="8" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="U23" s="8"/>
     </x:row>
@@ -4761,16 +4807,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F24" s="2" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="F24" s="2" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
         <x:v>1</x:v>
@@ -4782,7 +4828,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K24" s="3">
         <x:v>8</x:v>
@@ -4816,7 +4862,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T24" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="U24" s="2"/>
     </x:row>
@@ -4828,16 +4874,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D25" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E25" s="8" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="F25" s="8" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="G25" s="7" t="s">
         <x:v>1</x:v>
@@ -4849,7 +4895,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J25" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K25" s="7">
         <x:v>8</x:v>
@@ -4883,7 +4929,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T25" s="8" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="U25" s="8"/>
     </x:row>
@@ -4895,16 +4941,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="F26" s="2" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
         <x:v>1</x:v>
@@ -4916,7 +4962,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K26" s="3">
         <x:v>2</x:v>
@@ -4950,7 +4996,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorr, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T26" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="U26" s="2"/>
     </x:row>
@@ -4962,16 +5008,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D27" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="F27" s="8" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="G27" s="7" t="s">
         <x:v>1</x:v>
@@ -4983,7 +5029,7 @@
         <x:v>46196</x:v>
       </x:c>
       <x:c r="J27" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K27" s="7">
         <x:v>9</x:v>
@@ -5017,7 +5063,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T27" s="8" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="U27" s="8"/>
     </x:row>
@@ -5029,16 +5075,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F28" s="2" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="F28" s="2" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
         <x:v>1</x:v>
@@ -5050,7 +5096,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K28" s="3">
         <x:v>5</x:v>
@@ -5084,13 +5130,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector5, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T28" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="U28" s="2"/>
     </x:row>
     <x:row r="29" ht="22.049999237060547" customHeight="1">
       <x:c r="A29" s="44" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B29" s="44"/>
       <x:c r="C29" s="44"/>
@@ -5121,16 +5167,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D30" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E30" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F30" s="8" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="F30" s="8" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="G30" s="7" t="s">
         <x:v>1</x:v>
@@ -5142,7 +5188,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J30" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K30" s="7">
         <x:v>1</x:v>
@@ -5176,7 +5222,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T30" s="8" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="U30" s="8"/>
     </x:row>
@@ -5188,16 +5234,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E31" s="2" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F31" s="2" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="F31" s="2" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
         <x:v>1</x:v>
@@ -5209,7 +5255,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K31" s="3">
         <x:v>2</x:v>
@@ -5243,7 +5289,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_pos, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T31" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="U31" s="2"/>
     </x:row>
@@ -5255,16 +5301,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C32" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D32" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E32" s="8" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="F32" s="8" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="G32" s="7" t="s">
         <x:v>1</x:v>
@@ -5276,7 +5322,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J32" s="7" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K32" s="7">
         <x:v>1</x:v>
@@ -5310,7 +5356,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_name, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T32" s="8" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="U32" s="8"/>
     </x:row>
@@ -5322,16 +5368,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E33" s="2" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F33" s="2" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="F33" s="2" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
         <x:v>1</x:v>
@@ -5343,7 +5389,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K33" s="3">
         <x:v>2</x:v>
@@ -5377,7 +5423,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T33" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="U33" s="2"/>
     </x:row>
@@ -5389,16 +5435,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C34" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D34" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E34" s="8" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="F34" s="8" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="G34" s="7" t="s">
         <x:v>1</x:v>
@@ -5410,7 +5456,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J34" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K34" s="7">
         <x:v>7</x:v>
@@ -5444,7 +5490,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift8, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T34" s="8" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="U34" s="8"/>
     </x:row>
@@ -5456,16 +5502,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E35" s="2" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F35" s="2" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="F35" s="2" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
         <x:v>1</x:v>
@@ -5477,7 +5523,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K35" s="3">
         <x:v>1</x:v>
@@ -5511,7 +5557,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_add, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T35" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="U35" s="2"/>
     </x:row>
@@ -5523,16 +5569,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D36" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E36" s="8" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F36" s="8" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="F36" s="8" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="G36" s="7" t="s">
         <x:v>1</x:v>
@@ -5544,7 +5590,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J36" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="K36" s="7">
         <x:v>4</x:v>
@@ -5578,7 +5624,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_fadd, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T36" s="8" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U36" s="8"/>
     </x:row>
@@ -5590,16 +5636,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C37" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F37" s="2" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="F37" s="2" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
         <x:v>1</x:v>
@@ -5611,7 +5657,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K37" s="3">
         <x:v>2</x:v>
@@ -5645,7 +5691,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_cseladd, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T37" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="U37" s="2"/>
     </x:row>
@@ -5657,16 +5703,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D38" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E38" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="F38" s="8" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="G38" s="7" t="s">
         <x:v>1</x:v>
@@ -5678,7 +5724,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J38" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="K38" s="7">
         <x:v>1</x:v>
@@ -5712,13 +5758,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_addsub, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T38" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="U38" s="8"/>
     </x:row>
     <x:row r="39" ht="22.049999237060547" customHeight="1">
       <x:c r="A39" s="44" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B39" s="44"/>
       <x:c r="C39" s="44"/>
@@ -5749,16 +5795,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C40" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E40" s="2" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F40" s="2" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="F40" s="2" t="s">
-        <x:v>174</x:v>
       </x:c>
       <x:c r="G40" s="3" t="s">
         <x:v>1</x:v>
@@ -5770,7 +5816,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J40" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K40" s="3">
         <x:v>1</x:v>
@@ -5804,7 +5850,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T40" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="U40" s="2"/>
     </x:row>
@@ -5816,16 +5862,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C41" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D41" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E41" s="8" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="F41" s="8" t="s">
-        <x:v>178</x:v>
       </x:c>
       <x:c r="G41" s="7" t="s">
         <x:v>1</x:v>
@@ -5837,7 +5883,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J41" s="7" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K41" s="7">
         <x:v>1</x:v>
@@ -5871,7 +5917,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T41" s="8" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="U41" s="8"/>
     </x:row>
@@ -5883,16 +5929,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C42" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D42" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E42" s="2" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F42" s="2" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="F42" s="2" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="G42" s="3" t="s">
         <x:v>1</x:v>
@@ -5904,7 +5950,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J42" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="K42" s="3">
         <x:v>1</x:v>
@@ -5938,7 +5984,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T42" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="U42" s="2"/>
     </x:row>
@@ -5950,16 +5996,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D43" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E43" s="8" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F43" s="8" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="F43" s="8" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="G43" s="7" t="s">
         <x:v>1</x:v>
@@ -5971,7 +6017,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J43" s="7" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K43" s="7">
         <x:v>5</x:v>
@@ -6005,7 +6051,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T43" s="8" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="U43" s="8"/>
     </x:row>
@@ -6017,16 +6063,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C44" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D44" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E44" s="2" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F44" s="2" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="F44" s="2" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="G44" s="3" t="s">
         <x:v>1</x:v>
@@ -6038,7 +6084,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J44" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K44" s="3">
         <x:v>2</x:v>
@@ -6072,7 +6118,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T44" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="U44" s="2"/>
     </x:row>
@@ -6084,16 +6130,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D45" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E45" s="8" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F45" s="8" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="F45" s="8" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="G45" s="7" t="s">
         <x:v>1</x:v>
@@ -6105,7 +6151,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J45" s="7" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K45" s="7">
         <x:v>15</x:v>
@@ -6139,7 +6185,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T45" s="8" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="U45" s="8"/>
     </x:row>
@@ -6151,16 +6197,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D46" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E46" s="2" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F46" s="2" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="F46" s="2" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="G46" s="3" t="s">
         <x:v>1</x:v>
@@ -6172,7 +6218,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J46" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K46" s="3">
         <x:v>2</x:v>
@@ -6206,7 +6252,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_casez, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T46" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="U46" s="2"/>
     </x:row>
@@ -6218,16 +6264,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D47" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E47" s="8" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F47" s="8" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="F47" s="8" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="G47" s="7" t="s">
         <x:v>1</x:v>
@@ -6239,7 +6285,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J47" s="7" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K47" s="7">
         <x:v>3</x:v>
@@ -6273,13 +6319,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_nolatches, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T47" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="U47" s="8"/>
     </x:row>
     <x:row r="48" ht="22.049999237060547" customHeight="1">
       <x:c r="A48" s="44" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B48" s="44"/>
       <x:c r="C48" s="44"/>
@@ -6310,16 +6356,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C49" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D49" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E49" s="2" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F49" s="2" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="F49" s="2" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="G49" s="3" t="s">
         <x:v>1</x:v>
@@ -6331,7 +6377,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J49" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K49" s="3">
         <x:v>1</x:v>
@@ -6365,7 +6411,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/conditional, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T49" s="2" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="U49" s="2"/>
     </x:row>
@@ -6377,16 +6423,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D50" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E50" s="8" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F50" s="8" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="F50" s="8" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="G50" s="7" t="s">
         <x:v>1</x:v>
@@ -6398,7 +6444,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J50" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K50" s="7">
         <x:v>2</x:v>
@@ -6432,7 +6478,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/reduction, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T50" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="U50" s="8"/>
     </x:row>
@@ -6444,16 +6490,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C51" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D51" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E51" s="2" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F51" s="2" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="F51" s="2" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="G51" s="3" t="s">
         <x:v>1</x:v>
@@ -6465,7 +6511,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J51" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K51" s="3">
         <x:v>1</x:v>
@@ -6499,7 +6545,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates100, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T51" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="U51" s="2"/>
     </x:row>
@@ -6511,16 +6557,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E52" s="8" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F52" s="8" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="F52" s="8" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="G52" s="7" t="s">
         <x:v>1</x:v>
@@ -6532,7 +6578,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J52" s="7" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K52" s="7">
         <x:v>8</x:v>
@@ -6566,7 +6612,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector100r, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T52" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="U52" s="8"/>
     </x:row>
@@ -6578,16 +6624,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D53" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E53" s="2" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F53" s="2" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="F53" s="2" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="G53" s="3" t="s">
         <x:v>1</x:v>
@@ -6599,7 +6645,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J53" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K53" s="3">
         <x:v>22</x:v>
@@ -6633,7 +6679,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount255, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T53" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="U53" s="2"/>
     </x:row>
@@ -6645,16 +6691,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D54" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E54" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F54" s="8" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="F54" s="8" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="G54" s="7" t="s">
         <x:v>1</x:v>
@@ -6666,7 +6712,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J54" s="7" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K54" s="7">
         <x:v>19</x:v>
@@ -6700,7 +6746,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100i, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T54" s="8" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="U54" s="8"/>
     </x:row>
@@ -6712,16 +6758,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C55" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D55" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E55" s="2" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F55" s="2" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="F55" s="2" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="G55" s="3" t="s">
         <x:v>1</x:v>
@@ -6733,7 +6779,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J55" s="3" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K55" s="3">
         <x:v>6</x:v>
@@ -6767,13 +6813,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd100, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T55" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="U55" s="2"/>
     </x:row>
     <x:row r="56" ht="25.049999237060547" customHeight="1">
       <x:c r="A56" s="41" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B56" s="41"/>
       <x:c r="C56" s="41"/>
@@ -6798,7 +6844,7 @@
     </x:row>
     <x:row r="57" ht="22.049999237060547" customHeight="1">
       <x:c r="A57" s="44" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B57" s="44"/>
       <x:c r="C57" s="44"/>
@@ -6829,16 +6875,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D58" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D58" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E58" s="8" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F58" s="8" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="F58" s="8" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="G58" s="7" t="s">
         <x:v>1</x:v>
@@ -6850,7 +6896,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J58" s="7" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="K58" s="7">
         <x:v>1</x:v>
@@ -6884,7 +6930,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4h, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T58" s="8" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="U58" s="8"/>
     </x:row>
@@ -6896,16 +6942,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C59" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D59" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D59" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E59" s="2" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F59" s="2" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="F59" s="2" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="G59" s="3" t="s">
         <x:v>1</x:v>
@@ -6917,7 +6963,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J59" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K59" s="3">
         <x:v>1</x:v>
@@ -6951,7 +6997,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4i, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T59" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="U59" s="2"/>
     </x:row>
@@ -6963,16 +7009,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D60" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D60" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E60" s="8" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F60" s="8" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="F60" s="8" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="G60" s="7" t="s">
         <x:v>1</x:v>
@@ -6984,7 +7030,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J60" s="7" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K60" s="7">
         <x:v>2</x:v>
@@ -7018,7 +7064,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4e, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T60" s="8" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="U60" s="8"/>
     </x:row>
@@ -7030,16 +7076,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C61" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D61" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D61" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E61" s="2" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F61" s="2" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="F61" s="2" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="G61" s="3" t="s">
         <x:v>1</x:v>
@@ -7051,7 +7097,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J61" s="3" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K61" s="3">
         <x:v>1</x:v>
@@ -7085,7 +7131,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4f, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T61" s="2" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="U61" s="2"/>
     </x:row>
@@ -7097,16 +7143,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D62" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D62" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E62" s="8" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F62" s="8" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="F62" s="8" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="G62" s="7" t="s">
         <x:v>1</x:v>
@@ -7118,7 +7164,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J62" s="7" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="K62" s="7">
         <x:v>1</x:v>
@@ -7152,7 +7198,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4g, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T62" s="8" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="U62" s="8"/>
     </x:row>
@@ -7164,16 +7210,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C63" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D63" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D63" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E63" s="2" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F63" s="2" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="F63" s="2" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="G63" s="3" t="s">
         <x:v>1</x:v>
@@ -7185,7 +7231,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J63" s="3" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K63" s="3">
         <x:v>2</x:v>
@@ -7219,7 +7265,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T63" s="2" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="U63" s="2"/>
     </x:row>
@@ -7231,16 +7277,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D64" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D64" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E64" s="8" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F64" s="8" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="F64" s="8" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="G64" s="7" t="s">
         <x:v>1</x:v>
@@ -7252,7 +7298,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J64" s="7" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K64" s="7">
         <x:v>1</x:v>
@@ -7286,7 +7332,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7420, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T64" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="U64" s="8"/>
     </x:row>
@@ -7298,16 +7344,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C65" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D65" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D65" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E65" s="2" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F65" s="2" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="F65" s="2" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="G65" s="3" t="s">
         <x:v>1</x:v>
@@ -7319,7 +7365,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J65" s="3" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K65" s="3">
         <x:v>1</x:v>
@@ -7353,7 +7399,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/truthtable1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T65" s="2" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="U65" s="2"/>
     </x:row>
@@ -7365,16 +7411,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D66" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D66" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E66" s="8" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F66" s="8" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="F66" s="8" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G66" s="7" t="s">
         <x:v>1</x:v>
@@ -7386,7 +7432,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J66" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K66" s="7">
         <x:v>1</x:v>
@@ -7420,7 +7466,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_eq2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T66" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="U66" s="8"/>
     </x:row>
@@ -7432,16 +7478,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C67" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D67" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D67" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E67" s="2" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F67" s="2" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="F67" s="2" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="G67" s="3" t="s">
         <x:v>1</x:v>
@@ -7453,7 +7499,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J67" s="3" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="K67" s="3">
         <x:v>1</x:v>
@@ -7487,7 +7533,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4a, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T67" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="U67" s="2"/>
     </x:row>
@@ -7499,16 +7545,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C68" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D68" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D68" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E68" s="8" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F68" s="8" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="F68" s="8" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="G68" s="7" t="s">
         <x:v>1</x:v>
@@ -7520,7 +7566,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J68" s="7" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="K68" s="7">
         <x:v>1</x:v>
@@ -7554,7 +7600,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4b, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T68" s="8" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="U68" s="8"/>
     </x:row>
@@ -7566,16 +7612,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C69" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D69" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D69" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E69" s="2" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F69" s="2" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="F69" s="2" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="G69" s="3" t="s">
         <x:v>1</x:v>
@@ -7587,7 +7633,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J69" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="K69" s="3">
         <x:v>7</x:v>
@@ -7621,7 +7667,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T69" s="2" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="U69" s="2"/>
     </x:row>
@@ -7633,16 +7679,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D70" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D70" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E70" s="8" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F70" s="8" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="F70" s="8" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="G70" s="7" t="s">
         <x:v>1</x:v>
@@ -7654,7 +7700,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J70" s="7" t="s">
-        <x:v>286</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="K70" s="7">
         <x:v>5</x:v>
@@ -7688,7 +7734,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/ringer, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T70" s="8" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="U70" s="8"/>
     </x:row>
@@ -7700,16 +7746,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C71" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D71" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D71" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E71" s="2" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F71" s="2" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="F71" s="2" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="G71" s="3" t="s">
         <x:v>1</x:v>
@@ -7721,7 +7767,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J71" s="3" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="K71" s="3">
         <x:v>2</x:v>
@@ -7755,7 +7801,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/thermostat, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T71" s="2" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="U71" s="2"/>
     </x:row>
@@ -7767,16 +7813,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D72" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D72" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E72" s="8" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F72" s="8" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="F72" s="8" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="G72" s="7" t="s">
         <x:v>1</x:v>
@@ -7788,7 +7834,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J72" s="7" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K72" s="7">
         <x:v>2</x:v>
@@ -7822,7 +7868,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T72" s="8" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="U72" s="8"/>
     </x:row>
@@ -7834,16 +7880,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D73" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D73" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E73" s="2" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F73" s="2" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="F73" s="2" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="G73" s="3" t="s">
         <x:v>1</x:v>
@@ -7855,7 +7901,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J73" s="3" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="K73" s="3">
         <x:v>6</x:v>
@@ -7889,7 +7935,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T73" s="2" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="U73" s="2"/>
     </x:row>
@@ -7901,16 +7947,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C74" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D74" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D74" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E74" s="8" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F74" s="8" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="F74" s="8" t="s">
-        <x:v>301</x:v>
       </x:c>
       <x:c r="G74" s="7" t="s">
         <x:v>1</x:v>
@@ -7922,7 +7968,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J74" s="7" t="s">
-        <x:v>302</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="K74" s="7">
         <x:v>1</x:v>
@@ -7956,13 +8002,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv100, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T74" s="8" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="U74" s="8"/>
     </x:row>
     <x:row r="75" ht="22.049999237060547" customHeight="1">
       <x:c r="A75" s="44" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B75" s="44"/>
       <x:c r="C75" s="44"/>
@@ -7993,16 +8039,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C76" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D76" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E76" s="2" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F76" s="2" t="s">
         <x:v>305</x:v>
-      </x:c>
-      <x:c r="F76" s="2" t="s">
-        <x:v>306</x:v>
       </x:c>
       <x:c r="G76" s="3" t="s">
         <x:v>1</x:v>
@@ -8014,7 +8060,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J76" s="3" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="K76" s="3">
         <x:v>1</x:v>
@@ -8048,7 +8094,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T76" s="2" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="U76" s="2"/>
     </x:row>
@@ -8060,16 +8106,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C77" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D77" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E77" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F77" s="8" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="F77" s="8" t="s">
-        <x:v>310</x:v>
       </x:c>
       <x:c r="G77" s="7" t="s">
         <x:v>1</x:v>
@@ -8081,7 +8127,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J77" s="7" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="K77" s="7">
         <x:v>1</x:v>
@@ -8115,7 +8161,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1v, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T77" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="U77" s="8"/>
     </x:row>
@@ -8127,16 +8173,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C78" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D78" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E78" s="2" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F78" s="2" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="F78" s="2" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="G78" s="3" t="s">
         <x:v>1</x:v>
@@ -8148,7 +8194,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J78" s="3" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K78" s="3">
         <x:v>10</x:v>
@@ -8182,7 +8228,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux9to1v, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T78" s="2" t="s">
-        <x:v>316</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="U78" s="2"/>
     </x:row>
@@ -8194,16 +8240,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C79" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D79" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E79" s="8" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F79" s="8" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="F79" s="8" t="s">
-        <x:v>318</x:v>
       </x:c>
       <x:c r="G79" s="7" t="s">
         <x:v>1</x:v>
@@ -8215,7 +8261,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J79" s="7" t="s">
-        <x:v>319</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K79" s="7">
         <x:v>1</x:v>
@@ -8249,7 +8295,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T79" s="8" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="U79" s="8"/>
     </x:row>
@@ -8261,16 +8307,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C80" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D80" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E80" s="2" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="F80" s="2" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="F80" s="2" t="s">
-        <x:v>322</x:v>
       </x:c>
       <x:c r="G80" s="3" t="s">
         <x:v>1</x:v>
@@ -8282,7 +8328,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J80" s="3" t="s">
-        <x:v>323</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="K80" s="3">
         <x:v>1</x:v>
@@ -8316,13 +8362,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1v, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T80" s="2" t="s">
-        <x:v>324</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="U80" s="2"/>
     </x:row>
     <x:row r="81" ht="22.049999237060547" customHeight="1">
       <x:c r="A81" s="44" t="s">
-        <x:v>325</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B81" s="44"/>
       <x:c r="C81" s="44"/>
@@ -8353,16 +8399,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C82" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D82" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E82" s="8" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F82" s="8" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="F82" s="8" t="s">
-        <x:v>327</x:v>
       </x:c>
       <x:c r="G82" s="7" t="s">
         <x:v>1</x:v>
@@ -8374,7 +8420,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J82" s="7" t="s">
-        <x:v>328</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="K82" s="7">
         <x:v>1</x:v>
@@ -8408,7 +8454,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/hadd, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T82" s="8" t="s">
-        <x:v>329</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="U82" s="8"/>
     </x:row>
@@ -8420,16 +8466,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C83" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D83" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E83" s="2" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F83" s="2" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="F83" s="2" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="G83" s="3" t="s">
         <x:v>1</x:v>
@@ -8441,7 +8487,7 @@
         <x:v>46197</x:v>
       </x:c>
       <x:c r="J83" s="3" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="K83" s="3">
         <x:v>1</x:v>
@@ -8475,7 +8521,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fadd, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T83" s="2" t="s">
-        <x:v>333</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="U83" s="2"/>
     </x:row>
@@ -8487,16 +8533,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C84" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D84" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E84" s="8" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F84" s="8" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="F84" s="8" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="G84" s="7" t="s">
         <x:v>1</x:v>
@@ -8508,7 +8554,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J84" s="7" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="K84" s="7">
         <x:v>3</x:v>
@@ -8542,7 +8588,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T84" s="8" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="U84" s="8"/>
     </x:row>
@@ -8554,16 +8600,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D85" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E85" s="2" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F85" s="2" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="F85" s="2" t="s">
-        <x:v>339</x:v>
       </x:c>
       <x:c r="G85" s="3" t="s">
         <x:v>1</x:v>
@@ -8575,7 +8621,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J85" s="3" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="K85" s="3">
         <x:v>4</x:v>
@@ -8609,7 +8655,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4j, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T85" s="2" t="s">
-        <x:v>341</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="U85" s="2"/>
     </x:row>
@@ -8621,16 +8667,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C86" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D86" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E86" s="8" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="F86" s="8" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="F86" s="8" t="s">
-        <x:v>343</x:v>
       </x:c>
       <x:c r="G86" s="7" t="s">
         <x:v>1</x:v>
@@ -8642,7 +8688,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J86" s="7" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="K86" s="7">
         <x:v>1</x:v>
@@ -8676,7 +8722,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T86" s="8" t="s">
-        <x:v>345</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="U86" s="8"/>
     </x:row>
@@ -8688,16 +8734,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C87" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D87" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E87" s="2" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="F87" s="2" t="s">
         <x:v>346</x:v>
-      </x:c>
-      <x:c r="F87" s="2" t="s">
-        <x:v>347</x:v>
       </x:c>
       <x:c r="G87" s="3" t="s">
         <x:v>1</x:v>
@@ -8709,7 +8755,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J87" s="3" t="s">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="K87" s="3">
         <x:v>2</x:v>
@@ -8743,7 +8789,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T87" s="2" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="U87" s="2"/>
     </x:row>
@@ -8755,16 +8801,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C88" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D88" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E88" s="8" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="F88" s="8" t="s">
         <x:v>350</x:v>
-      </x:c>
-      <x:c r="F88" s="8" t="s">
-        <x:v>351</x:v>
       </x:c>
       <x:c r="G88" s="7" t="s">
         <x:v>1</x:v>
@@ -8776,7 +8822,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J88" s="7" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="K88" s="7">
         <x:v>2</x:v>
@@ -8810,13 +8856,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T88" s="8" t="s">
-        <x:v>353</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="U88" s="8"/>
     </x:row>
     <x:row r="89" ht="22.049999237060547" customHeight="1">
       <x:c r="A89" s="44" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B89" s="44"/>
       <x:c r="C89" s="44"/>
@@ -8847,16 +8893,16 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C90" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D90" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E90" s="2" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="F90" s="2" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="F90" s="2" t="s">
-        <x:v>356</x:v>
       </x:c>
       <x:c r="G90" s="3" t="s">
         <x:v>1</x:v>
@@ -8868,7 +8914,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J90" s="3" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="K90" s="3">
         <x:v>1</x:v>
@@ -8902,7 +8948,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T90" s="2" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="U90" s="2"/>
     </x:row>
@@ -8914,16 +8960,16 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C91" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D91" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E91" s="8" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F91" s="8" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="F91" s="8" t="s">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="G91" s="7" t="s">
         <x:v>1</x:v>
@@ -8935,7 +8981,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J91" s="7" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="K91" s="7">
         <x:v>1</x:v>
@@ -8969,7 +9015,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T91" s="8" t="s">
-        <x:v>362</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="U91" s="8"/>
     </x:row>
@@ -8981,16 +9027,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D92" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E92" s="2" t="s">
-        <x:v>359</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F92" s="2" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="G92" s="3" t="s">
         <x:v>1</x:v>
@@ -9002,7 +9048,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J92" s="3" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="K92" s="3">
         <x:v>4</x:v>
@@ -9036,7 +9082,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T92" s="2" t="s">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="U92" s="2"/>
     </x:row>
@@ -9048,16 +9094,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C93" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D93" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E93" s="8" t="s">
-        <x:v>359</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F93" s="8" t="s">
-        <x:v>366</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="G93" s="7" t="s">
         <x:v>1</x:v>
@@ -9069,7 +9115,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J93" s="7" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="K93" s="7">
         <x:v>1</x:v>
@@ -9103,7 +9149,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T93" s="8" t="s">
-        <x:v>368</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="U93" s="8"/>
     </x:row>
@@ -9115,16 +9161,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D94" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E94" s="2" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="F94" s="2" t="s">
         <x:v>369</x:v>
-      </x:c>
-      <x:c r="F94" s="2" t="s">
-        <x:v>370</x:v>
       </x:c>
       <x:c r="G94" s="3" t="s">
         <x:v>1</x:v>
@@ -9136,7 +9182,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J94" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="K94" s="3">
         <x:v>5</x:v>
@@ -9170,7 +9216,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T94" s="2" t="s">
-        <x:v>372</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="U94" s="2"/>
     </x:row>
@@ -9182,16 +9228,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C95" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D95" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E95" s="8" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="F95" s="8" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="F95" s="8" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G95" s="7" t="s">
         <x:v>1</x:v>
@@ -9203,7 +9249,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J95" s="7" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K95" s="7">
         <x:v>2</x:v>
@@ -9237,7 +9283,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T95" s="8" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="U95" s="8"/>
     </x:row>
@@ -9249,16 +9295,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C96" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D96" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E96" s="2" t="s">
-        <x:v>373</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F96" s="2" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="G96" s="3" t="s">
         <x:v>1</x:v>
@@ -9270,7 +9316,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J96" s="3" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="K96" s="3">
         <x:v>1</x:v>
@@ -9304,7 +9350,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q1g, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T96" s="2" t="s">
-        <x:v>379</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="U96" s="2"/>
     </x:row>
@@ -9316,16 +9362,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C97" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D97" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E97" s="8" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="F97" s="8" t="s">
         <x:v>380</x:v>
-      </x:c>
-      <x:c r="F97" s="8" t="s">
-        <x:v>381</x:v>
       </x:c>
       <x:c r="G97" s="7" t="s">
         <x:v>1</x:v>
@@ -9337,7 +9383,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J97" s="7" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="K97" s="7">
         <x:v>4</x:v>
@@ -9371,13 +9417,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T97" s="8" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="U97" s="8"/>
     </x:row>
     <x:row r="98" ht="22.049999237060547" customHeight="1">
       <x:c r="A98" s="44" t="s">
-        <x:v>384</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B98" s="44"/>
       <x:c r="C98" s="44"/>
@@ -9408,16 +9454,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C99" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D99" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E99" s="2" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="F99" s="2" t="s">
         <x:v>385</x:v>
-      </x:c>
-      <x:c r="F99" s="2" t="s">
-        <x:v>386</x:v>
       </x:c>
       <x:c r="G99" s="3" t="s">
         <x:v>1</x:v>
@@ -9429,7 +9475,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J99" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="K99" s="3">
         <x:v>1</x:v>
@@ -9463,7 +9509,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T99" s="2" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="U99" s="2"/>
     </x:row>
@@ -9475,16 +9521,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C100" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D100" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E100" s="8" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F100" s="8" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="F100" s="8" t="s">
-        <x:v>390</x:v>
       </x:c>
       <x:c r="G100" s="7" t="s">
         <x:v>1</x:v>
@@ -9496,7 +9542,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J100" s="7" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K100" s="7">
         <x:v>1</x:v>
@@ -9530,7 +9576,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T100" s="8" t="s">
-        <x:v>392</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="U100" s="8"/>
     </x:row>
@@ -9542,16 +9588,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="C101" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D101" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E101" s="2" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F101" s="2" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="F101" s="2" t="s">
-        <x:v>394</x:v>
       </x:c>
       <x:c r="G101" s="3" t="s">
         <x:v>1</x:v>
@@ -9563,7 +9609,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J101" s="3" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="K101" s="3">
         <x:v>2</x:v>
@@ -9597,7 +9643,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8r, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T101" s="2" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="U101" s="2"/>
     </x:row>
@@ -9609,16 +9655,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C102" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D102" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E102" s="8" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F102" s="8" t="s">
         <x:v>397</x:v>
-      </x:c>
-      <x:c r="F102" s="8" t="s">
-        <x:v>398</x:v>
       </x:c>
       <x:c r="G102" s="7" t="s">
         <x:v>1</x:v>
@@ -9630,7 +9676,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J102" s="7" t="s">
-        <x:v>399</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="K102" s="7">
         <x:v>2</x:v>
@@ -9664,7 +9710,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8p, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T102" s="8" t="s">
-        <x:v>400</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="U102" s="8"/>
     </x:row>
@@ -9676,16 +9722,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C103" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D103" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E103" s="2" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="F103" s="2" t="s">
         <x:v>401</x:v>
-      </x:c>
-      <x:c r="F103" s="2" t="s">
-        <x:v>402</x:v>
       </x:c>
       <x:c r="G103" s="3" t="s">
         <x:v>1</x:v>
@@ -9697,7 +9743,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J103" s="3" t="s">
-        <x:v>403</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="K103" s="3">
         <x:v>2</x:v>
@@ -9731,7 +9777,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8ar, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T103" s="2" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="U103" s="2"/>
     </x:row>
@@ -9743,16 +9789,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C104" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D104" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E104" s="8" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F104" s="8" t="s">
         <x:v>405</x:v>
-      </x:c>
-      <x:c r="F104" s="8" t="s">
-        <x:v>406</x:v>
       </x:c>
       <x:c r="G104" s="7" t="s">
         <x:v>1</x:v>
@@ -9764,7 +9810,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J104" s="7" t="s">
-        <x:v>407</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="K104" s="7">
         <x:v>9</x:v>
@@ -9798,7 +9844,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff16e, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T104" s="8" t="s">
-        <x:v>408</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="U104" s="8"/>
     </x:row>
@@ -9810,16 +9856,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C105" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D105" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E105" s="2" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="F105" s="2" t="s">
         <x:v>409</x:v>
-      </x:c>
-      <x:c r="F105" s="2" t="s">
-        <x:v>410</x:v>
       </x:c>
       <x:c r="G105" s="3" t="s">
         <x:v>1</x:v>
@@ -9831,7 +9877,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J105" s="3" t="s">
-        <x:v>411</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="K105" s="3">
         <x:v>8</x:v>
@@ -9865,7 +9911,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4a, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T105" s="2" t="s">
-        <x:v>412</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="U105" s="2"/>
     </x:row>
@@ -9877,16 +9923,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C106" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D106" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E106" s="8" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="F106" s="8" t="s">
         <x:v>413</x:v>
-      </x:c>
-      <x:c r="F106" s="8" t="s">
-        <x:v>414</x:v>
       </x:c>
       <x:c r="G106" s="7" t="s">
         <x:v>1</x:v>
@@ -9898,7 +9944,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J106" s="7" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="K106" s="7">
         <x:v>1</x:v>
@@ -9932,7 +9978,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4b, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T106" s="8" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="U106" s="8"/>
     </x:row>
@@ -9944,16 +9990,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C107" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D107" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E107" s="2" t="s">
-        <x:v>413</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="F107" s="2" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="G107" s="3" t="s">
         <x:v>1</x:v>
@@ -9965,7 +10011,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J107" s="3" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="K107" s="3">
         <x:v>1</x:v>
@@ -9999,7 +10045,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4c, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T107" s="2" t="s">
-        <x:v>419</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="U107" s="2"/>
     </x:row>
@@ -10011,16 +10057,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C108" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D108" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E108" s="8" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="F108" s="8" t="s">
         <x:v>420</x:v>
-      </x:c>
-      <x:c r="F108" s="8" t="s">
-        <x:v>421</x:v>
       </x:c>
       <x:c r="G108" s="7" t="s">
         <x:v>1</x:v>
@@ -10032,7 +10078,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J108" s="7" t="s">
-        <x:v>422</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="K108" s="7">
         <x:v>5</x:v>
@@ -10066,7 +10112,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4d, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T108" s="8" t="s">
-        <x:v>423</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="U108" s="8"/>
     </x:row>
@@ -10078,16 +10124,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C109" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D109" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E109" s="2" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="F109" s="2" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="F109" s="2" t="s">
-        <x:v>425</x:v>
       </x:c>
       <x:c r="G109" s="3" t="s">
         <x:v>1</x:v>
@@ -10099,7 +10145,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J109" s="3" t="s">
-        <x:v>426</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="K109" s="3">
         <x:v>2</x:v>
@@ -10133,7 +10179,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_muxdff, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T109" s="2" t="s">
-        <x:v>427</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="U109" s="2"/>
     </x:row>
@@ -10145,16 +10191,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C110" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D110" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E110" s="8" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F110" s="8" t="s">
-        <x:v>428</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="G110" s="7" t="s">
         <x:v>1</x:v>
@@ -10166,7 +10212,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J110" s="7" t="s">
-        <x:v>429</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="K110" s="7">
         <x:v>5</x:v>
@@ -10200,7 +10246,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4a, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T110" s="8" t="s">
-        <x:v>430</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="U110" s="8"/>
     </x:row>
@@ -10212,16 +10258,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C111" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D111" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E111" s="2" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="F111" s="2" t="s">
         <x:v>431</x:v>
-      </x:c>
-      <x:c r="F111" s="2" t="s">
-        <x:v>432</x:v>
       </x:c>
       <x:c r="G111" s="3" t="s">
         <x:v>1</x:v>
@@ -10233,7 +10279,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J111" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="K111" s="3">
         <x:v>3</x:v>
@@ -10267,7 +10313,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T111" s="2" t="s">
-        <x:v>434</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="U111" s="2"/>
     </x:row>
@@ -10279,16 +10325,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C112" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D112" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E112" s="8" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F112" s="8" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="F112" s="8" t="s">
-        <x:v>436</x:v>
       </x:c>
       <x:c r="G112" s="7" t="s">
         <x:v>1</x:v>
@@ -10300,7 +10346,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J112" s="7" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="K112" s="7">
         <x:v>1</x:v>
@@ -10334,7 +10380,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T112" s="8" t="s">
-        <x:v>438</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="U112" s="8"/>
     </x:row>
@@ -10346,16 +10392,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C113" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D113" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E113" s="2" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F113" s="2" t="s">
         <x:v>439</x:v>
-      </x:c>
-      <x:c r="F113" s="2" t="s">
-        <x:v>440</x:v>
       </x:c>
       <x:c r="G113" s="3" t="s">
         <x:v>1</x:v>
@@ -10367,7 +10413,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J113" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="K113" s="3">
         <x:v>1</x:v>
@@ -10401,7 +10447,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T113" s="2" t="s">
-        <x:v>442</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="U113" s="2"/>
     </x:row>
@@ -10413,16 +10459,16 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C114" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D114" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E114" s="8" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="F114" s="8" t="s">
         <x:v>443</x:v>
-      </x:c>
-      <x:c r="F114" s="8" t="s">
-        <x:v>444</x:v>
       </x:c>
       <x:c r="G114" s="7" t="s">
         <x:v>1</x:v>
@@ -10434,7 +10480,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J114" s="7" t="s">
-        <x:v>445</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="K114" s="7">
         <x:v>1</x:v>
@@ -10468,7 +10514,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T114" s="8" t="s">
-        <x:v>446</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="U114" s="8"/>
     </x:row>
@@ -10480,16 +10526,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="C115" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D115" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E115" s="2" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="F115" s="2" t="s">
         <x:v>447</x:v>
-      </x:c>
-      <x:c r="F115" s="2" t="s">
-        <x:v>448</x:v>
       </x:c>
       <x:c r="G115" s="3" t="s">
         <x:v>1</x:v>
@@ -10501,7 +10547,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J115" s="3" t="s">
-        <x:v>449</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="K115" s="3">
         <x:v>7</x:v>
@@ -10535,7 +10581,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgecapture, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T115" s="2" t="s">
-        <x:v>450</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="U115" s="2"/>
     </x:row>
@@ -10547,16 +10593,16 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="C116" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D116" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E116" s="8" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F116" s="8" t="s">
         <x:v>451</x:v>
-      </x:c>
-      <x:c r="F116" s="8" t="s">
-        <x:v>452</x:v>
       </x:c>
       <x:c r="G116" s="7" t="s">
         <x:v>1</x:v>
@@ -10568,7 +10614,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J116" s="7" t="s">
-        <x:v>453</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="K116" s="7">
         <x:v>7</x:v>
@@ -10602,13 +10648,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dualedge, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T116" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="U116" s="8"/>
     </x:row>
     <x:row r="117" ht="22.049999237060547" customHeight="1">
       <x:c r="A117" s="44" t="s">
-        <x:v>455</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B117" s="44"/>
       <x:c r="C117" s="44"/>
@@ -10639,16 +10685,16 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C118" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D118" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E118" s="2" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="F118" s="2" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="F118" s="2" t="s">
-        <x:v>457</x:v>
       </x:c>
       <x:c r="G118" s="3" t="s">
         <x:v>1</x:v>
@@ -10660,7 +10706,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J118" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="K118" s="3">
         <x:v>5</x:v>
@@ -10694,7 +10740,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count15, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T118" s="2" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="U118" s="2"/>
     </x:row>
@@ -10706,16 +10752,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C119" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D119" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E119" s="8" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="F119" s="8" t="s">
         <x:v>460</x:v>
-      </x:c>
-      <x:c r="F119" s="8" t="s">
-        <x:v>461</x:v>
       </x:c>
       <x:c r="G119" s="7" t="s">
         <x:v>1</x:v>
@@ -10727,7 +10773,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J119" s="7" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="K119" s="7">
         <x:v>3</x:v>
@@ -10761,7 +10807,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count10, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T119" s="8" t="s">
-        <x:v>463</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="U119" s="8"/>
     </x:row>
@@ -10773,16 +10819,16 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="C120" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D120" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E120" s="2" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="F120" s="2" t="s">
         <x:v>464</x:v>
-      </x:c>
-      <x:c r="F120" s="2" t="s">
-        <x:v>465</x:v>
       </x:c>
       <x:c r="G120" s="3" t="s">
         <x:v>1</x:v>
@@ -10794,7 +10840,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J120" s="3" t="s">
-        <x:v>466</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="K120" s="3">
         <x:v>3</x:v>
@@ -10828,7 +10874,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count1to10, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T120" s="2" t="s">
-        <x:v>467</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="U120" s="2"/>
     </x:row>
@@ -10840,16 +10886,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C121" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D121" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E121" s="8" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="F121" s="8" t="s">
         <x:v>468</x:v>
-      </x:c>
-      <x:c r="F121" s="8" t="s">
-        <x:v>469</x:v>
       </x:c>
       <x:c r="G121" s="7" t="s">
         <x:v>1</x:v>
@@ -10861,7 +10907,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J121" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="K121" s="7">
         <x:v>3</x:v>
@@ -10895,7 +10941,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/countslow, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T121" s="8" t="s">
-        <x:v>471</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="U121" s="8"/>
     </x:row>
@@ -10907,16 +10953,16 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="C122" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D122" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E122" s="2" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="F122" s="2" t="s">
         <x:v>472</x:v>
-      </x:c>
-      <x:c r="F122" s="2" t="s">
-        <x:v>473</x:v>
       </x:c>
       <x:c r="G122" s="3" t="s">
         <x:v>1</x:v>
@@ -10962,7 +11008,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7a, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T122" s="2" t="s">
-        <x:v>474</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="U122" s="2"/>
     </x:row>
@@ -10974,16 +11020,16 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="C123" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D123" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E123" s="8" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="F123" s="8" t="s">
         <x:v>475</x:v>
-      </x:c>
-      <x:c r="F123" s="8" t="s">
-        <x:v>476</x:v>
       </x:c>
       <x:c r="G123" s="7" t="s">
         <x:v>1</x:v>
@@ -11029,7 +11075,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7b, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T123" s="8" t="s">
-        <x:v>477</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="U123" s="8"/>
     </x:row>
@@ -11041,16 +11087,16 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="C124" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D124" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E124" s="2" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="F124" s="2" t="s">
         <x:v>478</x:v>
-      </x:c>
-      <x:c r="F124" s="2" t="s">
-        <x:v>479</x:v>
       </x:c>
       <x:c r="G124" s="3" t="s">
         <x:v>1</x:v>
@@ -11096,7 +11142,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/countbcd, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T124" s="2" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="U124" s="2"/>
     </x:row>
@@ -11108,16 +11154,16 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="C125" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D125" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E125" s="8" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="F125" s="8" t="s">
         <x:v>481</x:v>
-      </x:c>
-      <x:c r="F125" s="8" t="s">
-        <x:v>482</x:v>
       </x:c>
       <x:c r="G125" s="7" t="s">
         <x:v>1</x:v>
@@ -11163,13 +11209,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count_clock, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T125" s="8" t="s">
-        <x:v>483</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="U125" s="8"/>
     </x:row>
     <x:row r="126" ht="22.049999237060547" customHeight="1">
       <x:c r="A126" s="44" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B126" s="44"/>
       <x:c r="C126" s="44"/>
@@ -11200,16 +11246,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C127" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D127" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E127" s="2" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="F127" s="2" t="s">
         <x:v>485</x:v>
-      </x:c>
-      <x:c r="F127" s="2" t="s">
-        <x:v>486</x:v>
       </x:c>
       <x:c r="G127" s="3" t="s">
         <x:v>1</x:v>
@@ -11221,7 +11267,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J127" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="K127" s="3">
         <x:v>4</x:v>
@@ -11255,7 +11301,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T127" s="2" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="U127" s="2"/>
     </x:row>
@@ -11267,16 +11313,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C128" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D128" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E128" s="8" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="F128" s="8" t="s">
         <x:v>489</x:v>
-      </x:c>
-      <x:c r="F128" s="8" t="s">
-        <x:v>490</x:v>
       </x:c>
       <x:c r="G128" s="7" t="s">
         <x:v>1</x:v>
@@ -11288,7 +11334,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J128" s="7" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="K128" s="7">
         <x:v>2</x:v>
@@ -11322,7 +11368,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rotate100, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T128" s="8" t="s">
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="U128" s="8"/>
     </x:row>
@@ -11334,16 +11380,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="C129" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D129" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E129" s="2" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F129" s="2" t="s">
         <x:v>493</x:v>
-      </x:c>
-      <x:c r="F129" s="2" t="s">
-        <x:v>494</x:v>
       </x:c>
       <x:c r="G129" s="3" t="s">
         <x:v>1</x:v>
@@ -11355,7 +11401,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J129" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="K129" s="3">
         <x:v>6</x:v>
@@ -11389,7 +11435,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift18, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T129" s="2" t="s">
-        <x:v>496</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="U129" s="2"/>
     </x:row>
@@ -11401,16 +11447,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C130" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D130" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E130" s="8" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="F130" s="8" t="s">
         <x:v>497</x:v>
-      </x:c>
-      <x:c r="F130" s="8" t="s">
-        <x:v>498</x:v>
       </x:c>
       <x:c r="G130" s="7" t="s">
         <x:v>1</x:v>
@@ -11422,7 +11468,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J130" s="7" t="s">
-        <x:v>499</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="K130" s="7">
         <x:v>1</x:v>
@@ -11456,7 +11502,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr5, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T130" s="8" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="U130" s="8"/>
     </x:row>
@@ -11468,16 +11514,16 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C131" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D131" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E131" s="2" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="F131" s="2" t="s">
         <x:v>501</x:v>
-      </x:c>
-      <x:c r="F131" s="2" t="s">
-        <x:v>502</x:v>
       </x:c>
       <x:c r="G131" s="3" t="s">
         <x:v>1</x:v>
@@ -11489,7 +11535,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J131" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="K131" s="3">
         <x:v>4</x:v>
@@ -11523,7 +11569,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_lfsr, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T131" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="U131" s="2"/>
     </x:row>
@@ -11535,16 +11581,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C132" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D132" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E132" s="8" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="F132" s="8" t="s">
         <x:v>505</x:v>
-      </x:c>
-      <x:c r="F132" s="8" t="s">
-        <x:v>506</x:v>
       </x:c>
       <x:c r="G132" s="7" t="s">
         <x:v>1</x:v>
@@ -11556,7 +11602,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J132" s="7" t="s">
-        <x:v>507</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="K132" s="7">
         <x:v>1</x:v>
@@ -11590,7 +11636,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr32, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T132" s="8" t="s">
-        <x:v>508</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="U132" s="8"/>
     </x:row>
@@ -11602,16 +11648,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C133" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D133" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E133" s="2" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="F133" s="2" t="s">
         <x:v>509</x:v>
-      </x:c>
-      <x:c r="F133" s="2" t="s">
-        <x:v>510</x:v>
       </x:c>
       <x:c r="G133" s="3" t="s">
         <x:v>1</x:v>
@@ -11623,7 +11669,7 @@
         <x:v>46199</x:v>
       </x:c>
       <x:c r="J133" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="K133" s="3">
         <x:v>8</x:v>
@@ -11657,7 +11703,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4k, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T133" s="2" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="U133" s="2"/>
     </x:row>
@@ -11669,16 +11715,16 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C134" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D134" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E134" s="8" t="s">
-        <x:v>509</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F134" s="8" t="s">
-        <x:v>513</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="G134" s="7" t="s">
         <x:v>1</x:v>
@@ -11690,7 +11736,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J134" s="7" t="s">
-        <x:v>514</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="K134" s="7">
         <x:v>6</x:v>
@@ -11724,7 +11770,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4b, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T134" s="8" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="U134" s="8"/>
     </x:row>
@@ -11736,16 +11782,16 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="C135" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D135" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E135" s="2" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="F135" s="2" t="s">
         <x:v>516</x:v>
-      </x:c>
-      <x:c r="F135" s="2" t="s">
-        <x:v>517</x:v>
       </x:c>
       <x:c r="G135" s="3" t="s">
         <x:v>1</x:v>
@@ -11757,7 +11803,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J135" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="K135" s="3">
         <x:v>2</x:v>
@@ -11791,13 +11837,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T135" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="U135" s="2"/>
     </x:row>
     <x:row r="136" ht="22.049999237060547" customHeight="1">
       <x:c r="A136" s="44" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B136" s="44"/>
       <x:c r="C136" s="44"/>
@@ -11821,164 +11867,215 @@
       <x:c r="U136" s="44"/>
     </x:row>
     <x:row r="137" ht="34.04999923706055" customHeight="1">
-      <x:c r="A137" s="7">
+      <x:c r="A137" s="7" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B137" s="7"/>
-      <x:c r="C137" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D137" s="8" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E137" s="8" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="F137" s="8" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="G137" s="7" t="s">
-        <x:v>523</x:v>
+      <x:c r="B137" s="7" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C137" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D137" s="8" t="str">
+        <x:v>Sequential Logic → More Circuits</x:v>
+      </x:c>
+      <x:c r="E137" s="8" t="str">
+        <x:v>Rule 90</x:v>
+      </x:c>
+      <x:c r="F137" s="8" t="str">
+        <x:v>rule90</x:v>
+      </x:c>
+      <x:c r="G137" s="7" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H137" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I137" s="55"/>
-      <x:c r="J137" s="7"/>
-      <x:c r="K137" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L137" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M137" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N137" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O137" s="10"/>
-      <x:c r="P137" s="11"/>
-      <x:c r="Q137" s="11"/>
-      <x:c r="R137" s="11"/>
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="I137" s="55" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="J137" s="7" t="str">
+        <x:v>12:59:38 AM</x:v>
+      </x:c>
+      <x:c r="K137" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L137" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M137" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N137" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O137" s="10" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="P137" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/175-rule90.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/175-rule90.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q137" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/175-rule90-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/175-rule90-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R137" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/175-rule90.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/175-rule90.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S137" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rule90","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rule90, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T137" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T137" s="8" t="str">
+        <x:v>Rule 90 asks for a 512-cell one-dimensional cellular automaton. Each next cell is the XOR of the old left and right neighbors, with zero padding at both boundaries and synchronous load priority.</x:v>
       </x:c>
       <x:c r="U137" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Use nonblocking assignments so every cell reads the same pre-edge generation. Boundary cells need explicit zero neighbors; load must override evolution for the entire 512-bit row.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="34.04999923706055" customHeight="1">
-      <x:c r="A138" s="3">
+      <x:c r="A138" s="3" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B138" s="3"/>
-      <x:c r="C138" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D138" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E138" s="2" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="F138" s="2" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="G138" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B138" s="3" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C138" s="2" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D138" s="2" t="str">
+        <x:v>Sequential Logic → More Circuits</x:v>
+      </x:c>
+      <x:c r="E138" s="2" t="str">
+        <x:v>Rule 110</x:v>
+      </x:c>
+      <x:c r="F138" s="2" t="str">
+        <x:v>rule110</x:v>
+      </x:c>
+      <x:c r="G138" s="3" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H138" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I138" s="56"/>
-      <x:c r="J138" s="3"/>
-      <x:c r="K138" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L138" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M138" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N138" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O138" s="6"/>
-      <x:c r="P138" s="4"/>
-      <x:c r="Q138" s="4"/>
-      <x:c r="R138" s="4"/>
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="I138" s="56" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="J138" s="3" t="str">
+        <x:v>1:30:23 AM</x:v>
+      </x:c>
+      <x:c r="K138" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L138" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M138" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N138" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O138" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P138" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/176-rule110.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/176-rule110.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q138" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/176-rule110-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/176-rule110-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R138" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/176-rule110.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/176-rule110.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S138" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rule110","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rule110, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T138" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T138" s="2" t="str">
+        <x:v>Rule 110 asks for a 512-cell automaton where each next bit comes from the old left, center, and right neighborhood according to the Rule 110 truth table, with zero-padded edges.</x:v>
       </x:c>
       <x:c r="U138" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Translate the eight neighborhood cases directly and verify neighbor order. One clock edge advances one generation because all right-hand sides read old q before updates land.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="34.04999923706055" customHeight="1">
-      <x:c r="A139" s="7">
+      <x:c r="A139" s="7" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B139" s="7"/>
-      <x:c r="C139" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D139" s="8" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E139" s="8" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="F139" s="8" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="G139" s="7" t="s">
-        <x:v>523</x:v>
+      <x:c r="B139" s="7" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C139" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D139" s="8" t="str">
+        <x:v>Sequential Logic → More Circuits</x:v>
+      </x:c>
+      <x:c r="E139" s="8" t="str">
+        <x:v>Conway's Game of Life 16x16</x:v>
+      </x:c>
+      <x:c r="F139" s="8" t="str">
+        <x:v>conwaylife</x:v>
+      </x:c>
+      <x:c r="G139" s="7" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H139" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I139" s="55"/>
-      <x:c r="J139" s="7"/>
-      <x:c r="K139" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L139" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M139" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N139" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O139" s="10"/>
-      <x:c r="P139" s="11"/>
-      <x:c r="Q139" s="11"/>
-      <x:c r="R139" s="11"/>
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="I139" s="55" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="J139" s="7" t="str">
+        <x:v>1:36:17 PM</x:v>
+      </x:c>
+      <x:c r="K139" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L139" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M139" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N139" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O139" s="90" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="P139" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/179-conwaylife.md","Problem note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/179-conwaylife.md, friendlyName=Problem note</x:v>
+      </x:c>
+      <x:c r="Q139" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/179-conwaylife-question-and-successful-submission.png","Screenshot")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/179-conwaylife-question-and-successful-submission.png, friendlyName=Screenshot</x:v>
+      </x:c>
+      <x:c r="R139" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/179-conwaylife.sv","Solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/179-conwaylife.sv, friendlyName=Solution</x:v>
+      </x:c>
       <x:c r="S139" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/conwaylife","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/conwaylife, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T139" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T139" s="8" t="str">
+        <x:v>The Game of Life state is a 16 by 16 toroidal grid packed into `q[255:0]`, with each row occupying a 16-bit slice. A cell's next value depends on the count of its eight neighbours, while the load input synchronously replaces the whole grid with `data` for initialization. The toroidal boundary condition is the important part: row 0's upper neighbour is row 15, row 15's lower neighbour is row 0, column 0's left neighbour is column 15, and column 15's right neighbour is column 0. The implementation computes those wrapped row and column indices for every cell, accumulates the eight one-bit neighbour values into an integer count, and writes the corresponding bit of `next_q`. The update rule follows the problem statement exactly. A cell becomes alive when it has exactly three neighbours. With exactly two neighbours it keeps its previous state, so the expression is `neighbours == 3 || (q[index] &amp;&amp; neighbours == 2)`. All `next_q` bits are computed combinationally from the old registered `q`, then one clock edge commits the whole generation with a nonblocking assignment. This avoids accidentally updating one cell early and letting that new value affect another cell in the same generation.</x:v>
       </x:c>
       <x:c r="U139" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Toroidal wraparound is the key: compute wrapped row/column neighbours from the old q value, fill next_q combinationally, then commit the whole generation on the clock edge.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="22.049999237060547" customHeight="1">
       <x:c r="A140" s="44" t="s">
-        <x:v>529</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B140" s="44"/>
       <x:c r="C140" s="44"/>
@@ -12009,16 +12106,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C141" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D141" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E141" s="2" t="s">
-        <x:v>530</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="F141" s="2" t="s">
-        <x:v>531</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="G141" s="3" t="s">
         <x:v>1</x:v>
@@ -12030,7 +12127,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J141" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="K141" s="3">
         <x:v>9</x:v>
@@ -12064,7 +12161,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T141" s="2" t="s">
-        <x:v>533</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="U141" s="2"/>
     </x:row>
@@ -12076,16 +12173,16 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="C142" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D142" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E142" s="8" t="s">
-        <x:v>534</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F142" s="8" t="s">
-        <x:v>535</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="G142" s="7" t="s">
         <x:v>1</x:v>
@@ -12097,7 +12194,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J142" s="7" t="s">
-        <x:v>536</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="K142" s="7">
         <x:v>3</x:v>
@@ -12131,7 +12228,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1s, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T142" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="U142" s="8"/>
     </x:row>
@@ -12143,16 +12240,16 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="C143" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D143" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E143" s="2" t="s">
-        <x:v>538</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F143" s="2" t="s">
-        <x:v>539</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="G143" s="3" t="s">
         <x:v>1</x:v>
@@ -12164,7 +12261,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J143" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="K143" s="3">
         <x:v>6</x:v>
@@ -12198,7 +12295,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T143" s="2" t="s">
-        <x:v>541</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="U143" s="2"/>
     </x:row>
@@ -12210,16 +12307,16 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="C144" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D144" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E144" s="8" t="s">
-        <x:v>542</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="F144" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="G144" s="7" t="s">
         <x:v>1</x:v>
@@ -12231,7 +12328,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J144" s="7" t="s">
-        <x:v>544</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="K144" s="7">
         <x:v>2</x:v>
@@ -12265,7 +12362,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2s, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T144" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="U144" s="8"/>
     </x:row>
@@ -12277,16 +12374,16 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="C145" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D145" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E145" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F145" s="2" t="s">
-        <x:v>547</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="G145" s="3" t="s">
         <x:v>1</x:v>
@@ -12298,7 +12395,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J145" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="K145" s="3">
         <x:v>7</x:v>
@@ -12332,7 +12429,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3comb, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T145" s="2" t="s">
-        <x:v>549</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="U145" s="2"/>
     </x:row>
@@ -12344,16 +12441,16 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="C146" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D146" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E146" s="8" t="s">
-        <x:v>550</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F146" s="8" t="s">
-        <x:v>551</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="G146" s="7" t="s">
         <x:v>1</x:v>
@@ -12365,7 +12462,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J146" s="7" t="s">
-        <x:v>552</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="K146" s="7">
         <x:v>6</x:v>
@@ -12399,7 +12496,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3onehot, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T146" s="8" t="s">
-        <x:v>553</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="U146" s="8"/>
     </x:row>
@@ -12411,16 +12508,16 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C147" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D147" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E147" s="2" t="s">
-        <x:v>554</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F147" s="2" t="s">
-        <x:v>555</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="G147" s="3" t="s">
         <x:v>1</x:v>
@@ -12432,7 +12529,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J147" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="K147" s="3">
         <x:v>1</x:v>
@@ -12466,7 +12563,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T147" s="2" t="s">
-        <x:v>557</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="U147" s="2"/>
     </x:row>
@@ -12478,16 +12575,16 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="C148" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D148" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E148" s="8" t="s">
-        <x:v>558</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F148" s="8" t="s">
-        <x:v>559</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="G148" s="7" t="s">
         <x:v>1</x:v>
@@ -12499,7 +12596,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J148" s="7" t="s">
-        <x:v>560</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="K148" s="7">
         <x:v>2</x:v>
@@ -12533,7 +12630,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3s, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T148" s="8" t="s">
-        <x:v>561</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="U148" s="8"/>
     </x:row>
@@ -12545,16 +12642,16 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="C149" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D149" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E149" s="2" t="s">
-        <x:v>562</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F149" s="2" t="s">
-        <x:v>563</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="G149" s="3" t="s">
         <x:v>1</x:v>
@@ -12566,7 +12663,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J149" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="K149" s="3">
         <x:v>4</x:v>
@@ -12600,7 +12697,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T149" s="2" t="s">
-        <x:v>565</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="U149" s="2"/>
     </x:row>
@@ -12612,16 +12709,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="C150" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D150" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E150" s="8" t="s">
-        <x:v>566</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F150" s="8" t="s">
-        <x:v>567</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="G150" s="7" t="s">
         <x:v>1</x:v>
@@ -12633,7 +12730,7 @@
         <x:v>46200</x:v>
       </x:c>
       <x:c r="J150" s="7" t="s">
-        <x:v>568</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="K150" s="7">
         <x:v>2</x:v>
@@ -12667,7 +12764,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T150" s="8" t="s">
-        <x:v>569</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="U150" s="8"/>
     </x:row>
@@ -12675,528 +12772,690 @@
       <x:c r="A151" s="3">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B151" s="3"/>
+      <x:c r="B151" s="3" t="n">
+        <x:v>159</x:v>
+      </x:c>
       <x:c r="C151" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D151" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E151" s="2" t="s">
-        <x:v>570</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F151" s="2" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="G151" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H151" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I151" s="56"/>
-      <x:c r="J151" s="3"/>
-      <x:c r="K151" s="3">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="G151" s="3" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H151" s="91" t="str">
+        <x:v>Day 11</x:v>
+      </x:c>
+      <x:c r="I151" s="56" t="n">
+        <x:v>46207</x:v>
+      </x:c>
+      <x:c r="J151" s="3" t="str">
+        <x:v>5:14:31 PM</x:v>
+      </x:c>
+      <x:c r="K151" s="3" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L151" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M151" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L151" s="3">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M151" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N151" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O151" s="6">
-        <x:v>0</x:v>
+      <x:c r="N151" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O151" s="88" t="n">
+        <x:v>0.047619047619047616</x:v>
       </x:c>
       <x:c r="P151" s="4" t="e">
-        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/Review.md","Review")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/Review.md, friendlyName=Review</x:v>
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/159-lemmings2.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/159-lemmings2.md, friendlyName=Note</x:v>
       </x:c>
       <x:c r="Q151" s="4" t="e">
-        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Review/120-lemmings2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Review/120-lemmings2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R151" s="4"/>
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/159-lemmings2-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/159-lemmings2-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R151" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/159-lemmings2.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/159-lemmings2.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S151" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings2","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings2, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T151" s="2" t="s">
-        <x:v>572</x:v>
+      <x:c r="T151" s="2" t="str">
+        <x:v>Extend the walking-direction FSM with direction-preserving falling states that ignore bumps and resume the remembered direction on landing.</x:v>
       </x:c>
       <x:c r="U151" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Use four Moore states for walking/falling × left/right. Ground loss has priority, each register has one owner, and outputs decode registered state.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="34.04999923706055" customHeight="1">
       <x:c r="A152" s="7">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B152" s="7"/>
+      <x:c r="B152" s="7" t="n">
+        <x:v>160</x:v>
+      </x:c>
       <x:c r="C152" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D152" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E152" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F152" s="8" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="G152" s="7" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H152" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I152" s="55"/>
-      <x:c r="J152" s="7"/>
-      <x:c r="K152" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L152" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M152" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N152" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O152" s="10"/>
-      <x:c r="P152" s="11"/>
-      <x:c r="Q152" s="11"/>
-      <x:c r="R152" s="11"/>
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G152" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H152" s="91" t="str">
+        <x:v>Day 11</x:v>
+      </x:c>
+      <x:c r="I152" s="55" t="n">
+        <x:v>46207</x:v>
+      </x:c>
+      <x:c r="J152" s="7" t="str">
+        <x:v>5:57:22 PM</x:v>
+      </x:c>
+      <x:c r="K152" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L152" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M152" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N152" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O152" s="90" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="P152" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/160-lemmings3.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/160-lemmings3.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q152" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/160-lemmings3-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/160-lemmings3-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R152" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/160-lemmings3.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/160-lemmings3.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S152" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings3","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings3, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T152" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T152" s="8" t="str">
+        <x:v>Add persistent digging behavior while preserving direction across the fall that begins when digging removes the ground.</x:v>
       </x:c>
       <x:c r="U152" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Dig is a transition command, not a sustained enable. Direction-specific digging and falling states preserve history while ignoring irrelevant bumps.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="34.04999923706055" customHeight="1">
       <x:c r="A153" s="3">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B153" s="3"/>
+      <x:c r="B153" s="3" t="n">
+        <x:v>161</x:v>
+      </x:c>
       <x:c r="C153" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D153" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E153" s="2" t="s">
-        <x:v>575</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F153" s="2" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G153" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H153" s="57" t="str">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="G153" s="3" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H153" s="91" t="str">
         <x:v>Day 12</x:v>
       </x:c>
-      <x:c r="I153" s="56"/>
-      <x:c r="J153" s="3"/>
-      <x:c r="K153" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L153" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M153" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N153" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O153" s="6"/>
-      <x:c r="P153" s="4"/>
-      <x:c r="Q153" s="4"/>
-      <x:c r="R153" s="4"/>
+      <x:c r="I153" s="56" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="J153" s="3" t="str">
+        <x:v>1:10:55 PM</x:v>
+      </x:c>
+      <x:c r="K153" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L153" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M153" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N153" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O153" s="88" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="P153" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/161-lemmings4.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/161-lemmings4.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q153" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/161-lemmings4-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/161-lemmings4-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R153" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/161-lemmings4.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/161-lemmings4.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S153" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings4","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings4, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T153" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T153" s="2" t="str">
+        <x:v>Add a fall-duration limit so a Lemming that falls for more than 20 cycles enters a permanent splatter state.</x:v>
       </x:c>
       <x:c r="U153" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Keep phase in FSM state and duration in a saturating counter. Test the counter when landing and make splatter an absorbing state.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="34.04999923706055" customHeight="1">
       <x:c r="A154" s="7">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B154" s="7"/>
+      <x:c r="B154" s="7" t="n">
+        <x:v>162</x:v>
+      </x:c>
       <x:c r="C154" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D154" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E154" s="8" t="s">
-        <x:v>577</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="F154" s="8" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="G154" s="7" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H154" s="57" t="str">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="G154" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H154" s="91" t="str">
         <x:v>Day 12</x:v>
       </x:c>
-      <x:c r="I154" s="55"/>
-      <x:c r="J154" s="7"/>
-      <x:c r="K154" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L154" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M154" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N154" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O154" s="10"/>
-      <x:c r="P154" s="11"/>
-      <x:c r="Q154" s="11"/>
-      <x:c r="R154" s="11"/>
+      <x:c r="I154" s="55" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="J154" s="7" t="str">
+        <x:v>5:09:39 PM</x:v>
+      </x:c>
+      <x:c r="K154" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L154" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M154" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N154" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O154" s="90" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="P154" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/162-fsm_onehot.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/162-fsm_onehot.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q154" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/162-fsm_onehot-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/162-fsm_onehot-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R154" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/162-fsm_onehot.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/162-fsm_onehot.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S154" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_onehot","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_onehot, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T154" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T154" s="8" t="str">
+        <x:v>Derive ten one-hot next-state equations and two output equations directly from the supplied state diagram without adding state storage.</x:v>
       </x:c>
       <x:c r="U154" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Preserve the supplied state[9:0] interface. Each destination bit is the OR of its incoming enabled arcs; parameters cannot alias run-time state bits.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="34.04999923706055" customHeight="1">
       <x:c r="A155" s="3">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B155" s="3"/>
+      <x:c r="B155" s="3" t="n">
+        <x:v>166</x:v>
+      </x:c>
       <x:c r="C155" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D155" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E155" s="2" t="s">
-        <x:v>579</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F155" s="2" t="s">
-        <x:v>580</x:v>
-      </x:c>
-      <x:c r="G155" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H155" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I155" s="56"/>
-      <x:c r="J155" s="3"/>
-      <x:c r="K155" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L155" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M155" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N155" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O155" s="6"/>
-      <x:c r="P155" s="4"/>
-      <x:c r="Q155" s="4"/>
-      <x:c r="R155" s="4"/>
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="G155" s="3" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H155" s="91" t="str">
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I155" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J155" s="3" t="str">
+        <x:v>2:56:49 PM</x:v>
+      </x:c>
+      <x:c r="K155" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L155" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M155" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N155" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O155" s="88" t="n">
+        <x:v>0.2727272727272727</x:v>
+      </x:c>
+      <x:c r="P155" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/166-fsm_ps2.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/166-fsm_ps2.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q155" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/166-fsm_ps2-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/166-fsm_ps2-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R155" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/166-fsm_ps2.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/166-fsm_ps2.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S155" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_ps2","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_ps2, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T155" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T155" s="2" t="str">
+        <x:v>Detect the first byte of a three-byte PS/2 packet using in[3], consume the next two bytes, and pulse done.</x:v>
       </x:c>
       <x:c r="U155" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>The input is one byte per clock. Only byte 1 is detected by content; bytes 2 and 3 are positional, and the done-cycle input may begin the next packet.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="34.04999923706055" customHeight="1">
       <x:c r="A156" s="7">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B156" s="7"/>
+      <x:c r="B156" s="7" t="n">
+        <x:v>167</x:v>
+      </x:c>
       <x:c r="C156" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D156" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E156" s="8" t="s">
-        <x:v>581</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F156" s="8" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="G156" s="7" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H156" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I156" s="55"/>
-      <x:c r="J156" s="7"/>
-      <x:c r="K156" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L156" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M156" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N156" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O156" s="10"/>
-      <x:c r="P156" s="11"/>
-      <x:c r="Q156" s="11"/>
-      <x:c r="R156" s="11"/>
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="G156" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H156" s="91" t="str">
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I156" s="55" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J156" s="7" t="str">
+        <x:v>3:28:06 PM</x:v>
+      </x:c>
+      <x:c r="K156" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L156" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M156" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N156" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O156" s="90" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="P156" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/167-fsm_ps2data.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/167-fsm_ps2data.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q156" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/167-fsm_ps2data-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/167-fsm_ps2data-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R156" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/167-fsm_ps2data.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/167-fsm_ps2data.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S156" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_ps2data","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_ps2data, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T156" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T156" s="8" t="str">
+        <x:v>Store the three PS/2 bytes in out_bytes[23:16], [15:8], and [7:0] while supporting back-to-back packets.</x:v>
       </x:c>
       <x:c r="U156" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>A scalar index selects one bit; whole bytes need fixed part-selects. Capture byte 1 in start/done on the same edge that recognizes it.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="34.04999923706055" customHeight="1">
       <x:c r="A157" s="3">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B157" s="3"/>
+      <x:c r="B157" s="3" t="n">
+        <x:v>163</x:v>
+      </x:c>
       <x:c r="C157" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D157" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E157" s="2" t="s">
-        <x:v>583</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F157" s="2" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="G157" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H157" s="57" t="str">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G157" s="3" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H157" s="91" t="str">
         <x:v>Day 12</x:v>
       </x:c>
-      <x:c r="I157" s="56"/>
-      <x:c r="J157" s="3"/>
-      <x:c r="K157" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L157" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M157" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N157" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O157" s="6"/>
-      <x:c r="P157" s="4"/>
-      <x:c r="Q157" s="4"/>
-      <x:c r="R157" s="4"/>
+      <x:c r="I157" s="56" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="J157" s="3" t="str">
+        <x:v>11:29:35 PM</x:v>
+      </x:c>
+      <x:c r="K157" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L157" s="3" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M157" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N157" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O157" s="88" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="P157" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/163-fsm_serial.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/163-fsm_serial.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q157" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/163-fsm_serial-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/163-fsm_serial-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R157" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/163-fsm_serial.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/163-fsm_serial.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S157" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serial","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serial, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T157" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T157" s="2" t="str">
+        <x:v>Recognize a low start bit, eight data bits, and a high stop bit; pulse done and recover correctly after a malformed stop bit.</x:v>
       </x:c>
       <x:c r="U157" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Count only data cycles, decode done from a completed state, and wait for idle high in an error state before accepting a new frame.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="34.04999923706055" customHeight="1">
       <x:c r="A158" s="7">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B158" s="7"/>
+      <x:c r="B158" s="7" t="n">
+        <x:v>164</x:v>
+      </x:c>
       <x:c r="C158" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D158" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E158" s="8" t="s">
-        <x:v>585</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F158" s="8" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="G158" s="7" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H158" s="57" t="str">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="G158" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H158" s="91" t="str">
         <x:v>Day 12</x:v>
       </x:c>
-      <x:c r="I158" s="55"/>
-      <x:c r="J158" s="7"/>
-      <x:c r="K158" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L158" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M158" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N158" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O158" s="10"/>
-      <x:c r="P158" s="11"/>
-      <x:c r="Q158" s="11"/>
-      <x:c r="R158" s="11"/>
+      <x:c r="I158" s="55" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="J158" s="7" t="str">
+        <x:v>11:48:46 PM</x:v>
+      </x:c>
+      <x:c r="K158" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L158" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M158" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N158" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O158" s="90" t="n">
+        <x:v>0.09090909090909091</x:v>
+      </x:c>
+      <x:c r="P158" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/164-fsm_serialdata.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/164-fsm_serialdata.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q158" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/164-fsm_serialdata-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/164-fsm_serialdata-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R158" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/164-fsm_serialdata.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/164-fsm_serialdata.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S158" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serialdata","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serialdata, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T158" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T158" s="8" t="str">
+        <x:v>Add an LSB-first byte datapath to the serial-frame FSM and present the reconstructed byte when done is asserted.</x:v>
       </x:c>
       <x:c r="U158" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Control decides when bits are data; latch[count] stores LSB-first bits directly. The first mismatch localized the bug to stop/done cycle alignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="34.04999923706055" customHeight="1">
       <x:c r="A159" s="3">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B159" s="3"/>
+      <x:c r="B159" s="3" t="n">
+        <x:v>165</x:v>
+      </x:c>
       <x:c r="C159" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D159" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E159" s="2" t="s">
-        <x:v>587</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="F159" s="2" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="G159" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H159" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I159" s="56"/>
-      <x:c r="J159" s="3"/>
-      <x:c r="K159" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L159" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M159" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N159" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O159" s="6"/>
-      <x:c r="P159" s="4"/>
-      <x:c r="Q159" s="4"/>
-      <x:c r="R159" s="4"/>
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="G159" s="3" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H159" s="91" t="str">
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I159" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J159" s="3" t="str">
+        <x:v>1:59:50 PM</x:v>
+      </x:c>
+      <x:c r="K159" s="3" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L159" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M159" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N159" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O159" s="88" t="n">
+        <x:v>0.2857142857142857</x:v>
+      </x:c>
+      <x:c r="P159" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/165-fsm_serialdp.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/165-fsm_serialdp.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q159" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/165-fsm_serialdp-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/165-fsm_serialdp-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R159" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/165-fsm_serialdp.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/165-fsm_serialdp.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S159" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serialdp","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serialdp, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T159" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T159" s="2" t="str">
+        <x:v>Extend the serial receiver with odd-parity checking over eight data bits plus the parity bit, accepting only a valid stop bit and parity.</x:v>
       </x:c>
       <x:c r="U159" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Reset parity per frame, accumulate data plus parity, and use a separate parity state so parity and stop bits cannot be confused.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="34.04999923706055" customHeight="1">
       <x:c r="A160" s="7">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B160" s="7"/>
+      <x:c r="B160" s="7" t="n">
+        <x:v>168</x:v>
+      </x:c>
       <x:c r="C160" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D160" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E160" s="8" t="s">
-        <x:v>589</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="F160" s="8" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="G160" s="7" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H160" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I160" s="55"/>
-      <x:c r="J160" s="7"/>
-      <x:c r="K160" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L160" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M160" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N160" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O160" s="10"/>
-      <x:c r="P160" s="11"/>
-      <x:c r="Q160" s="11"/>
-      <x:c r="R160" s="11"/>
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="G160" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H160" s="91" t="str">
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I160" s="55" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J160" s="7" t="str">
+        <x:v>4:21:20 PM</x:v>
+      </x:c>
+      <x:c r="K160" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L160" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M160" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N160" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O160" s="90" t="n">
+        <x:v>0.16666666666666666</x:v>
+      </x:c>
+      <x:c r="P160" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/168-fsm_hdlc.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/168-fsm_hdlc.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q160" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/168-fsm_hdlc-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/168-fsm_hdlc-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R160" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/168-fsm_hdlc.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/168-fsm_hdlc.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S160" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_hdlc","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_hdlc, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T160" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T160" s="8" t="str">
+        <x:v>Recognize HDLC discard, flag, and error patterns from consecutive-one runs and produce correctly timed output pulses.</x:v>
       </x:c>
       <x:c r="U160" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Label states by exact run length. Zero after five ones is discard, zero after six is flag, and a seventh one is error; this fixes the early pulse.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="34.04999923706055" customHeight="1">
@@ -13207,16 +13466,16 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C161" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D161" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E161" s="2" t="s">
-        <x:v>591</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F161" s="2" t="s">
-        <x:v>592</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="G161" s="3" t="s">
         <x:v>1</x:v>
@@ -13228,7 +13487,7 @@
         <x:v>46202</x:v>
       </x:c>
       <x:c r="J161" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="K161" s="3">
         <x:v>12</x:v>
@@ -13262,112 +13521,146 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q8, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T161" s="2" t="s">
-        <x:v>594</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="U161" s="2"/>
     </x:row>
     <x:row r="162" ht="34.04999923706055" customHeight="1">
-      <x:c r="A162" s="7">
+      <x:c r="A162" s="7" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B162" s="7"/>
-      <x:c r="C162" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D162" s="8" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E162" s="8" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="F162" s="8" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="G162" s="7" t="s">
-        <x:v>523</x:v>
+      <x:c r="B162" s="7" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C162" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D162" s="8" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E162" s="8" t="str">
+        <x:v>Q5a: Serial two's complementer (Moore FSM)</x:v>
+      </x:c>
+      <x:c r="F162" s="8" t="str">
+        <x:v>exams/ece241_2014_q5a</x:v>
+      </x:c>
+      <x:c r="G162" s="7" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H162" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I162" s="55"/>
-      <x:c r="J162" s="7"/>
-      <x:c r="K162" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L162" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M162" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N162" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O162" s="10"/>
-      <x:c r="P162" s="11"/>
-      <x:c r="Q162" s="11"/>
-      <x:c r="R162" s="11"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I162" s="55" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J162" s="7" t="str">
+        <x:v>6:24:56 PM</x:v>
+      </x:c>
+      <x:c r="K162" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L162" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M162" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N162" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O162" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P162" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/169-exams__ece241_2014_q5a.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/169-exams__ece241_2014_q5a.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q162" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/169-exams__ece241_2014_q5a-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/169-exams__ece241_2014_q5a-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R162" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/169-exams__ece241_2014_q5a.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/169-exams__ece241_2014_q5a.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S162" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5a","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5a, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T162" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T162" s="8" t="str">
+        <x:v>Implement a Moore serial two's-complementer that copies bits through the first 1 and inverts every later bit while processing the word least-significant bit first.</x:v>
       </x:c>
       <x:c r="U162" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Moore output timing is state-only, so the state history must account for the first-1 boundary without letting the current input drive z combinationally.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="34.04999923706055" customHeight="1">
-      <x:c r="A163" s="3">
+      <x:c r="A163" s="3" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B163" s="3"/>
-      <x:c r="C163" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D163" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E163" s="2" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="F163" s="2" t="s">
-        <x:v>598</x:v>
-      </x:c>
-      <x:c r="G163" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B163" s="3" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C163" s="2" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D163" s="2" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E163" s="2" t="str">
+        <x:v>Q5b: Serial two's complementer (Mealy FSM)</x:v>
+      </x:c>
+      <x:c r="F163" s="2" t="str">
+        <x:v>exams/ece241_2014_q5b</x:v>
+      </x:c>
+      <x:c r="G163" s="3" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H163" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I163" s="56"/>
-      <x:c r="J163" s="3"/>
-      <x:c r="K163" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L163" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M163" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N163" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O163" s="6"/>
-      <x:c r="P163" s="4"/>
-      <x:c r="Q163" s="4"/>
-      <x:c r="R163" s="4"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I163" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J163" s="3" t="str">
+        <x:v>6:50:12 PM</x:v>
+      </x:c>
+      <x:c r="K163" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L163" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M163" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N163" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O163" s="6" t="n">
+        <x:v>0.16666666666666666</x:v>
+      </x:c>
+      <x:c r="P163" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/170-exams__ece241_2014_q5b.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/170-exams__ece241_2014_q5b.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q163" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/170-exams__ece241_2014_q5b-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/170-exams__ece241_2014_q5b-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R163" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/170-exams__ece241_2014_q5b.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/170-exams__ece241_2014_q5b.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S163" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5b","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5b, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T163" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T163" s="2" t="str">
+        <x:v>Implement the Mealy version of the serial two's-complementer, where output depends on both the stored history and the current input bit.</x:v>
       </x:c>
       <x:c r="U163" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>The Mealy form emits the first copied 1 in the same cycle that transitions into the invert-after-first-one state, reducing the state burden compared with the Moore version.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="34.04999923706055" customHeight="1">
@@ -13378,16 +13671,16 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="C164" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D164" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E164" s="8" t="s">
-        <x:v>599</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="F164" s="8" t="s">
-        <x:v>600</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="G164" s="7" t="str">
         <x:v>Completed</x:v>
@@ -13447,16 +13740,16 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="C165" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D165" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E165" s="2" t="s">
-        <x:v>601</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="F165" s="2" t="s">
-        <x:v>602</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="G165" s="3" t="str">
         <x:v>Completed</x:v>
@@ -13516,16 +13809,16 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="C166" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D166" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E166" s="8" t="s">
-        <x:v>603</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="F166" s="8" t="s">
-        <x:v>604</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="G166" s="7" t="str">
         <x:v>Completed</x:v>
@@ -13578,55 +13871,72 @@
       </x:c>
     </x:row>
     <x:row r="167" ht="34.04999923706055" customHeight="1">
-      <x:c r="A167" s="3">
+      <x:c r="A167" s="3" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B167" s="3"/>
-      <x:c r="C167" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D167" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E167" s="2" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="F167" s="2" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="G167" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B167" s="3" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C167" s="2" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D167" s="2" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E167" s="2" t="str">
+        <x:v>Q6b: FSM next-state logic</x:v>
+      </x:c>
+      <x:c r="F167" s="2" t="str">
+        <x:v>exams/m2014_q6b</x:v>
+      </x:c>
+      <x:c r="G167" s="3" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H167" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I167" s="56"/>
-      <x:c r="J167" s="3"/>
-      <x:c r="K167" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L167" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M167" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N167" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O167" s="6"/>
-      <x:c r="P167" s="4"/>
-      <x:c r="Q167" s="4"/>
-      <x:c r="R167" s="4"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I167" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J167" s="3" t="str">
+        <x:v>9:53:56 PM</x:v>
+      </x:c>
+      <x:c r="K167" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L167" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M167" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N167" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O167" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P167" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/171-exams__m2014_q6b.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/171-exams__m2014_q6b.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q167" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/171-exams__m2014_q6b-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/171-exams__m2014_q6b-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R167" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/171-exams__m2014_q6b.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/171-exams__m2014_q6b.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S167" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q6b","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q6b, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T167" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T167" s="2" t="str">
+        <x:v>Derive one FSM next-state equation by collecting every incoming transition to the requested destination state and ORing the enabled product terms.</x:v>
       </x:c>
       <x:c r="U167" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Read arrows by destination, not by source. The reliable method is to list incoming arcs first, then simplify only after every self-loop and input polarity is accounted for.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="34.04999923706055" customHeight="1">
@@ -13637,16 +13947,16 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="C168" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D168" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E168" s="8" t="s">
-        <x:v>607</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F168" s="8" t="s">
-        <x:v>608</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="G168" s="7" t="str">
         <x:v>Completed</x:v>
@@ -13699,219 +14009,279 @@
       </x:c>
     </x:row>
     <x:row r="169" ht="34.04999923706055" customHeight="1">
-      <x:c r="A169" s="3">
+      <x:c r="A169" s="3" t="n">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B169" s="3"/>
-      <x:c r="C169" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D169" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E169" s="2" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="F169" s="2" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="G169" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B169" s="3" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C169" s="2" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D169" s="2" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E169" s="2" t="str">
+        <x:v>Q6: FSM</x:v>
+      </x:c>
+      <x:c r="F169" s="2" t="str">
+        <x:v>exams/m2014_q6</x:v>
+      </x:c>
+      <x:c r="G169" s="3" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H169" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I169" s="56"/>
-      <x:c r="J169" s="3"/>
-      <x:c r="K169" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L169" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M169" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N169" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O169" s="6"/>
-      <x:c r="P169" s="4"/>
-      <x:c r="Q169" s="4"/>
-      <x:c r="R169" s="4"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I169" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J169" s="3" t="str">
+        <x:v>10:01:46 PM</x:v>
+      </x:c>
+      <x:c r="K169" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L169" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M169" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N169" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O169" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P169" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/172-exams__m2014_q6.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/172-exams__m2014_q6.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q169" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/172-exams__m2014_q6-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/172-exams__m2014_q6-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R169" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/172-exams__m2014_q6.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/172-exams__m2014_q6.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S169" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q6","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q6, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T169" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T169" s="2" t="str">
+        <x:v>Build the complete FSM from the given transition diagram, including synchronous reset, registered state progression, combinational next-state logic, and Moore output decode.</x:v>
       </x:c>
       <x:c r="U169" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Separating state register, transition logic, and output decode makes reset timing and Moore output timing explicit and avoids accidental latch behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="34.04999923706055" customHeight="1">
-      <x:c r="A170" s="7">
+      <x:c r="A170" s="7" t="n">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B170" s="7"/>
-      <x:c r="C170" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D170" s="8" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E170" s="8" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="F170" s="8" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="G170" s="7" t="s">
-        <x:v>523</x:v>
+      <x:c r="B170" s="7" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C170" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D170" s="8" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E170" s="8" t="str">
+        <x:v>Q2a: FSM</x:v>
+      </x:c>
+      <x:c r="F170" s="8" t="str">
+        <x:v>exams/2012_q2fsm</x:v>
+      </x:c>
+      <x:c r="G170" s="7" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H170" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I170" s="55"/>
-      <x:c r="J170" s="7"/>
-      <x:c r="K170" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L170" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M170" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N170" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O170" s="10"/>
-      <x:c r="P170" s="11"/>
-      <x:c r="Q170" s="11"/>
-      <x:c r="R170" s="11"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I170" s="55" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J170" s="7" t="str">
+        <x:v>10:06:12 PM</x:v>
+      </x:c>
+      <x:c r="K170" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L170" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M170" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N170" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O170" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P170" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/173-exams__2012_q2fsm.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/173-exams__2012_q2fsm.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q170" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/173-exams__2012_q2fsm-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/173-exams__2012_q2fsm-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R170" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/173-exams__2012_q2fsm.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/173-exams__2012_q2fsm.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S170" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q2fsm","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q2fsm, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T170" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T170" s="8" t="str">
+        <x:v>Implement the state diagram as a conventional Moore FSM with reset, registered state, complete transition cases, and output decoded from the present state.</x:v>
       </x:c>
       <x:c r="U170" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Trace the diagram one row at a time and then run a full sequence trace to catch one-cycle Moore output mistakes and reversed transition branches.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="34.04999923706055" customHeight="1">
-      <x:c r="A171" s="3">
+      <x:c r="A171" s="3" t="n">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B171" s="3"/>
-      <x:c r="C171" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D171" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E171" s="2" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="F171" s="2" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="G171" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B171" s="3" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C171" s="2" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D171" s="2" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E171" s="2" t="str">
+        <x:v>Q2b: One-hot FSM equations</x:v>
+      </x:c>
+      <x:c r="F171" s="2" t="str">
+        <x:v>exams/2012_q2b</x:v>
+      </x:c>
+      <x:c r="G171" s="3" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H171" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I171" s="56"/>
-      <x:c r="J171" s="3"/>
-      <x:c r="K171" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L171" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M171" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N171" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O171" s="6"/>
-      <x:c r="P171" s="4"/>
-      <x:c r="Q171" s="4"/>
-      <x:c r="R171" s="4"/>
+        <x:v>Day 13</x:v>
+      </x:c>
+      <x:c r="I171" s="56" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="J171" s="3" t="str">
+        <x:v>10:38:05 PM</x:v>
+      </x:c>
+      <x:c r="K171" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L171" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M171" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N171" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O171" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P171" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/174-exams__2012_q2b.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/174-exams__2012_q2b.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q171" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/174-exams__2012_q2b-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/174-exams__2012_q2b-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R171" s="4" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/174-exams__2012_q2b.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/174-exams__2012_q2b.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S171" s="4" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q2b","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q2b, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T171" s="2" t="s">
-        <x:v>524</x:v>
+      <x:c r="T171" s="2" t="str">
+        <x:v>Write direct one-hot next-state and output equations from the same FSM, using the supplied present-state vector rather than building a state register.</x:v>
       </x:c>
       <x:c r="U171" s="2" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>For one-hot equations, each destination bit is an OR of incoming transition terms. This avoids priority-case behavior and keeps every arrow represented exactly once.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="34.04999923706055" customHeight="1">
-      <x:c r="A172" s="7">
+      <x:c r="A172" s="7" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B172" s="7"/>
-      <x:c r="C172" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D172" s="8" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E172" s="8" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="F172" s="8" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="G172" s="7" t="s">
+      <x:c r="B172" s="7" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C172" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D172" s="8" t="str">
+        <x:v>Sequential Logic → Finite State Machines</x:v>
+      </x:c>
+      <x:c r="E172" s="8" t="str">
+        <x:v>Q2a: FSM</x:v>
+      </x:c>
+      <x:c r="F172" s="8" t="str">
+        <x:v>exams/2013_q2afsm</x:v>
+      </x:c>
+      <x:c r="G172" s="7" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H172" s="57" t="str">
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="I172" s="55" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="J172" s="7" t="str">
+        <x:v>1:36:14 AM</x:v>
+      </x:c>
+      <x:c r="K172" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L172" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M172" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H172" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I172" s="55"/>
-      <x:c r="J172" s="7"/>
-      <x:c r="K172" s="7">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L172" s="7">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M172" s="7">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N172" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O172" s="10">
-        <x:v>0</x:v>
+      <x:c r="N172" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O172" s="10" t="n">
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="P172" s="11" t="e">
-        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/Review.md","Review")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/Review.md, friendlyName=Review</x:v>
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/177-exams__2013_q2afsm.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/177-exams__2013_q2afsm.md, friendlyName=Note</x:v>
       </x:c>
       <x:c r="Q172" s="11" t="e">
-        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Review/review-exams__2013_q2afsm.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Review/review-exams__2013_q2afsm.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R172" s="11"/>
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/177-exams__2013_q2afsm-question-and-successful-submission.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/177-exams__2013_q2afsm-question-and-successful-submission.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R172" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/177-exams__2013_q2afsm.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/177-exams__2013_q2afsm.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S172" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2013_q2afsm","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2013_q2afsm, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T172" s="8" t="s">
-        <x:v>616</x:v>
+      <x:c r="T172" s="8" t="str">
+        <x:v>Implement an arbiter FSM whose registered state selects idle or one active requester, follows the request-priority transition diagram, and decodes mutually exclusive grants.</x:v>
       </x:c>
       <x:c r="U172" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>The repaired solution covers every request combination, holds a grant while its request remains asserted, returns to idle on withdrawal, and keeps prior failed evidence as revision context.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="34.04999923706055" customHeight="1">
@@ -13922,16 +14292,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C173" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D173" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E173" s="2" t="s">
-        <x:v>617</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="F173" s="2" t="s">
-        <x:v>618</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="G173" s="3" t="s">
         <x:v>1</x:v>
@@ -13943,7 +14313,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J173" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="K173" s="3">
         <x:v>2</x:v>
@@ -13977,13 +14347,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2013_q2bfsm, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T173" s="2" t="s">
-        <x:v>620</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="U173" s="2"/>
     </x:row>
     <x:row r="174" ht="22.049999237060547" customHeight="1">
       <x:c r="A174" s="44" t="s">
-        <x:v>621</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B174" s="44"/>
       <x:c r="C174" s="44"/>
@@ -14014,16 +14384,16 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="C175" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D175" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E175" s="8" t="s">
-        <x:v>622</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="F175" s="8" t="s">
-        <x:v>623</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="G175" s="7" t="s">
         <x:v>1</x:v>
@@ -14069,7 +14439,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_count1k, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T175" s="8" t="s">
-        <x:v>624</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="U175" s="8"/>
     </x:row>
@@ -14081,16 +14451,16 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="C176" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D176" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E176" s="2" t="s">
-        <x:v>625</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F176" s="2" t="s">
-        <x:v>626</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="G176" s="3" t="s">
         <x:v>1</x:v>
@@ -14136,7 +14506,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_shiftcount, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T176" s="2" t="s">
-        <x:v>627</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="U176" s="2"/>
     </x:row>
@@ -14148,16 +14518,16 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="C177" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D177" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E177" s="8" t="s">
-        <x:v>628</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F177" s="8" t="s">
-        <x:v>629</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="G177" s="7" t="s">
         <x:v>1</x:v>
@@ -14203,7 +14573,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmseq, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T177" s="8" t="s">
-        <x:v>630</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="U177" s="8"/>
     </x:row>
@@ -14215,16 +14585,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="C178" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D178" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E178" s="2" t="s">
-        <x:v>631</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F178" s="2" t="s">
-        <x:v>632</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="G178" s="3" t="s">
         <x:v>1</x:v>
@@ -14270,7 +14640,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmshift, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T178" s="2" t="s">
-        <x:v>633</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="U178" s="2"/>
     </x:row>
@@ -14409,60 +14779,77 @@
       <x:c r="U180" s="2"/>
     </x:row>
     <x:row r="181" ht="34.04999923706055" customHeight="1">
-      <x:c r="A181" s="7">
+      <x:c r="A181" s="7" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B181" s="7"/>
-      <x:c r="C181" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D181" s="8" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E181" s="8" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="F181" s="8" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="G181" s="7" t="s">
-        <x:v>523</x:v>
+      <x:c r="B181" s="7" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C181" s="8" t="str">
+        <x:v>Circuits</x:v>
+      </x:c>
+      <x:c r="D181" s="8" t="str">
+        <x:v>Building Larger Circuits</x:v>
+      </x:c>
+      <x:c r="E181" s="8" t="str">
+        <x:v>FSM: One-hot logic equations</x:v>
+      </x:c>
+      <x:c r="F181" s="8" t="str">
+        <x:v>exams/review2015_fsmonehot</x:v>
+      </x:c>
+      <x:c r="G181" s="7" t="str">
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H181" s="57" t="str">
-        <x:v>Day 12</x:v>
-      </x:c>
-      <x:c r="I181" s="55"/>
-      <x:c r="J181" s="7"/>
-      <x:c r="K181" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L181" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M181" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N181" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O181" s="10"/>
-      <x:c r="P181" s="11"/>
-      <x:c r="Q181" s="11"/>
-      <x:c r="R181" s="11"/>
+        <x:v>Day 14</x:v>
+      </x:c>
+      <x:c r="I181" s="55" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="J181" s="7" t="str">
+        <x:v>12:49:56 PM</x:v>
+      </x:c>
+      <x:c r="K181" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L181" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M181" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N181" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O181" s="90" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P181" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/178-exams__review2015_fsmonehot.md","Problem note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/178-exams__review2015_fsmonehot.md, friendlyName=Problem note</x:v>
+      </x:c>
+      <x:c r="Q181" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/178-exams__review2015_fsmonehot-question-and-successful-submission.png","Screenshot")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/178-exams__review2015_fsmonehot-question-and-successful-submission.png, friendlyName=Screenshot</x:v>
+      </x:c>
+      <x:c r="R181" s="11" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/178-exams__review2015_fsmonehot.sv","Solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/178-exams__review2015_fsmonehot.sv, friendlyName=Solution</x:v>
+      </x:c>
       <x:c r="S181" s="11" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fsmonehot","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmonehot, friendlyName=HDLBits</x:v>
       </x:c>
-      <x:c r="T181" s="8" t="s">
-        <x:v>524</x:v>
+      <x:c r="T181" s="8" t="str">
+        <x:v>This exercise extracts only selected one-hot equations from the complete timer controller. The supplied `state[9:0]` vector already represents the present state, so the module must not create a state register or recode the FSM. Each requested `*_next` output is the OR of every transition entering that destination state. For example, `B3_next` is high only when the current state is `B2`, because the B0-B3 shift phase advances unconditionally one state per clock. `Count_next` is high when the current state is `B3` or when the controller is already in `Count` and `done_counting` is still low. `Wait_next` is high when counting has just completed or when the controller is already waiting and `ack` has not arrived. The output equations are direct Moore decodes from the current one-hot state: `done` is `state[Wait]`, `counting` is `state[Count]`, and `shift_ena` is the OR of B0 through B3. The key review habit is destination-first derivation: list incoming arrows for each requested destination bit and translate those arrows directly into sum-of-products logic.</x:v>
       </x:c>
       <x:c r="U181" s="8" t="str">
-        <x:v>Planned for 2026-07-05. Add the screenshot, solution, archive number, and actual submission timestamp only after HDLBits reports Success.</x:v>
+        <x:v>Use destination-first one-hot equations. HDLBits asks for selected next-state bits and outputs only, so an unused state-bit warning can be correct after a successful submission.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="25.049999237060547" customHeight="1">
       <x:c r="A182" s="41" t="s">
-        <x:v>636</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B182" s="41"/>
       <x:c r="C182" s="41"/>
@@ -14487,7 +14874,7 @@
     </x:row>
     <x:row r="183" ht="22.049999237060547" customHeight="1">
       <x:c r="A183" s="44" t="s">
-        <x:v>637</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B183" s="44"/>
       <x:c r="C183" s="44"/>
@@ -14518,16 +14905,16 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="C184" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D184" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D184" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E184" s="2" t="s">
-        <x:v>638</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F184" s="2" t="s">
-        <x:v>639</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="G184" s="3" t="s">
         <x:v>1</x:v>
@@ -14539,7 +14926,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J184" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="K184" s="3">
         <x:v>4</x:v>
@@ -14573,7 +14960,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_mux2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T184" s="2" t="s">
-        <x:v>641</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="U184" s="2"/>
     </x:row>
@@ -14585,16 +14972,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="C185" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D185" s="8" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D185" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E185" s="8" t="s">
-        <x:v>642</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F185" s="8" t="s">
-        <x:v>643</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="G185" s="7" t="s">
         <x:v>1</x:v>
@@ -14606,7 +14993,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J185" s="7" t="s">
-        <x:v>644</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="K185" s="7">
         <x:v>2</x:v>
@@ -14640,7 +15027,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_nand3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T185" s="8" t="s">
-        <x:v>645</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="U185" s="8"/>
     </x:row>
@@ -14652,16 +15039,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="C186" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D186" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D186" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E186" s="2" t="s">
-        <x:v>638</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F186" s="2" t="s">
-        <x:v>646</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="G186" s="3" t="s">
         <x:v>1</x:v>
@@ -14673,7 +15060,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J186" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="K186" s="3">
         <x:v>7</x:v>
@@ -14707,7 +15094,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_mux4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T186" s="2" t="s">
-        <x:v>648</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="U186" s="2"/>
     </x:row>
@@ -14719,16 +15106,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="C187" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D187" s="8" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D187" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E187" s="8" t="s">
-        <x:v>649</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F187" s="8" t="s">
-        <x:v>650</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="G187" s="7" t="s">
         <x:v>1</x:v>
@@ -14740,7 +15127,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J187" s="7" t="s">
-        <x:v>651</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="K187" s="7">
         <x:v>12</x:v>
@@ -14774,7 +15161,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_addsubz, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T187" s="8" t="s">
-        <x:v>652</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="U187" s="8"/>
     </x:row>
@@ -14786,16 +15173,16 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="C188" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D188" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D188" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E188" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F188" s="2" t="s">
-        <x:v>653</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="G188" s="3" t="s">
         <x:v>1</x:v>
@@ -14807,7 +15194,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J188" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="K188" s="3">
         <x:v>5</x:v>
@@ -14841,13 +15228,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_case, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T188" s="2" t="s">
-        <x:v>655</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="U188" s="2"/>
     </x:row>
     <x:row r="189" ht="22.049999237060547" customHeight="1">
       <x:c r="A189" s="44" t="s">
-        <x:v>656</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B189" s="44"/>
       <x:c r="C189" s="44"/>
@@ -14878,16 +15265,16 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="C190" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D190" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E190" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="F190" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="G190" s="7" t="s">
         <x:v>1</x:v>
@@ -14899,7 +15286,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J190" s="7" t="s">
-        <x:v>659</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K190" s="7">
         <x:v>2</x:v>
@@ -14933,7 +15320,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T190" s="8" t="s">
-        <x:v>660</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="U190" s="8"/>
     </x:row>
@@ -14945,16 +15332,16 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="C191" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D191" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E191" s="2" t="s">
-        <x:v>661</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="F191" s="2" t="s">
-        <x:v>662</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="G191" s="3" t="s">
         <x:v>1</x:v>
@@ -14966,7 +15353,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J191" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="K191" s="3">
         <x:v>2</x:v>
@@ -15000,7 +15387,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T191" s="2" t="s">
-        <x:v>664</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="U191" s="2"/>
     </x:row>
@@ -15012,16 +15399,16 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="C192" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D192" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E192" s="8" t="s">
-        <x:v>665</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="F192" s="8" t="s">
-        <x:v>666</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="G192" s="7" t="s">
         <x:v>1</x:v>
@@ -15033,7 +15420,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J192" s="7" t="s">
-        <x:v>667</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="K192" s="7">
         <x:v>1</x:v>
@@ -15067,7 +15454,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit3, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T192" s="8" t="s">
-        <x:v>668</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="U192" s="8"/>
     </x:row>
@@ -15079,16 +15466,16 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="C193" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D193" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E193" s="2" t="s">
-        <x:v>669</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="F193" s="2" t="s">
-        <x:v>670</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="G193" s="3" t="s">
         <x:v>1</x:v>
@@ -15100,7 +15487,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J193" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="K193" s="3">
         <x:v>4</x:v>
@@ -15134,7 +15521,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit4, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T193" s="2" t="s">
-        <x:v>672</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="U193" s="2"/>
     </x:row>
@@ -15146,16 +15533,16 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="C194" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D194" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E194" s="8" t="s">
-        <x:v>673</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="F194" s="8" t="s">
-        <x:v>674</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="G194" s="7" t="s">
         <x:v>1</x:v>
@@ -15167,7 +15554,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J194" s="7" t="s">
-        <x:v>675</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="K194" s="7">
         <x:v>4</x:v>
@@ -15201,7 +15588,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit5, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T194" s="8" t="s">
-        <x:v>676</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="U194" s="8"/>
     </x:row>
@@ -15213,16 +15600,16 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="C195" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D195" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E195" s="2" t="s">
-        <x:v>677</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="F195" s="2" t="s">
-        <x:v>678</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="G195" s="3" t="s">
         <x:v>1</x:v>
@@ -15234,7 +15621,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J195" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="K195" s="3">
         <x:v>2</x:v>
@@ -15268,7 +15655,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit6, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T195" s="2" t="s">
-        <x:v>680</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="U195" s="2"/>
     </x:row>
@@ -15280,16 +15667,16 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="C196" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D196" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E196" s="8" t="s">
-        <x:v>681</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="F196" s="8" t="s">
-        <x:v>682</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="G196" s="7" t="s">
         <x:v>1</x:v>
@@ -15301,7 +15688,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J196" s="7" t="s">
-        <x:v>683</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="K196" s="7">
         <x:v>5</x:v>
@@ -15335,7 +15722,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit7, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T196" s="8" t="s">
-        <x:v>684</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="U196" s="8"/>
     </x:row>
@@ -15347,16 +15734,16 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="C197" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D197" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E197" s="2" t="s">
-        <x:v>685</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="F197" s="2" t="s">
-        <x:v>686</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="G197" s="3" t="s">
         <x:v>1</x:v>
@@ -15368,7 +15755,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J197" s="3" t="s">
-        <x:v>323</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="K197" s="3">
         <x:v>18</x:v>
@@ -15402,7 +15789,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit8, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T197" s="2" t="s">
-        <x:v>687</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="U197" s="2"/>
     </x:row>
@@ -15414,16 +15801,16 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="C198" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D198" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E198" s="8" t="s">
-        <x:v>688</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="F198" s="8" t="s">
-        <x:v>689</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="G198" s="7" t="s">
         <x:v>1</x:v>
@@ -15435,7 +15822,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J198" s="7" t="s">
-        <x:v>690</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="K198" s="7">
         <x:v>3</x:v>
@@ -15469,7 +15856,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit9, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T198" s="8" t="s">
-        <x:v>691</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="U198" s="8"/>
     </x:row>
@@ -15481,16 +15868,16 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="C199" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D199" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E199" s="2" t="s">
-        <x:v>692</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="F199" s="2" t="s">
-        <x:v>693</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="G199" s="3" t="s">
         <x:v>1</x:v>
@@ -15502,7 +15889,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J199" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="K199" s="3">
         <x:v>1</x:v>
@@ -15536,13 +15923,13 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit10, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T199" s="2" t="s">
-        <x:v>695</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="U199" s="2"/>
     </x:row>
     <x:row r="200" ht="25.049999237060547" customHeight="1">
       <x:c r="A200" s="41" t="s">
-        <x:v>696</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B200" s="41"/>
       <x:c r="C200" s="41"/>
@@ -15573,14 +15960,14 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="C201" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D201" s="8"/>
       <x:c r="E201" s="8" t="s">
-        <x:v>697</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="F201" s="8" t="s">
-        <x:v>698</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="G201" s="7" t="s">
         <x:v>1</x:v>
@@ -15592,7 +15979,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J201" s="7" t="s">
-        <x:v>699</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="K201" s="7">
         <x:v>5</x:v>
@@ -15626,7 +16013,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/clock, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T201" s="8" t="s">
-        <x:v>700</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="U201" s="8"/>
     </x:row>
@@ -15638,14 +16025,14 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="C202" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D202" s="2"/>
       <x:c r="E202" s="2" t="s">
-        <x:v>701</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="F202" s="2" t="s">
-        <x:v>702</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="G202" s="3" t="s">
         <x:v>1</x:v>
@@ -15657,7 +16044,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J202" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="K202" s="3">
         <x:v>4</x:v>
@@ -15691,7 +16078,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tb1, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T202" s="2" t="s">
-        <x:v>704</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="U202" s="2"/>
     </x:row>
@@ -15703,14 +16090,14 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="C203" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D203" s="8"/>
       <x:c r="E203" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F203" s="8" t="s">
-        <x:v>705</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="G203" s="7" t="s">
         <x:v>1</x:v>
@@ -15722,7 +16109,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J203" s="7" t="s">
-        <x:v>706</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="K203" s="7">
         <x:v>7</x:v>
@@ -15756,7 +16143,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/and, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T203" s="8" t="s">
-        <x:v>707</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="U203" s="8"/>
     </x:row>
@@ -15768,14 +16155,14 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="C204" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D204" s="2"/>
       <x:c r="E204" s="2" t="s">
-        <x:v>708</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="F204" s="2" t="s">
-        <x:v>709</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="G204" s="3" t="s">
         <x:v>1</x:v>
@@ -15787,7 +16174,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J204" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="K204" s="3">
         <x:v>7</x:v>
@@ -15821,7 +16208,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tb2, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T204" s="2" t="s">
-        <x:v>711</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="U204" s="2"/>
     </x:row>
@@ -15833,14 +16220,14 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="C205" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D205" s="13"/>
       <x:c r="E205" s="13" t="s">
-        <x:v>712</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="F205" s="13" t="s">
-        <x:v>713</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="G205" s="12" t="s">
         <x:v>1</x:v>
@@ -15852,7 +16239,7 @@
         <x:v>46201</x:v>
       </x:c>
       <x:c r="J205" s="12" t="s">
-        <x:v>714</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="K205" s="12">
         <x:v>9</x:v>
@@ -15886,7 +16273,7 @@
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tff, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T205" s="13" t="s">
-        <x:v>715</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="U205" s="13"/>
     </x:row>
